--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rcb50215a37fb4076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹测算" sheetId="2" r:id="R6df3cdb0a3a8442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内外盘曲线" sheetId="3" r:id="Rc561d916392a4ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗筹明细" sheetId="4" r:id="Rc06c2cd2ebfe4d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数与来源" sheetId="5" r:id="Rf606e03640024b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rffe7e1a924f44acc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹测算" sheetId="2" r:id="Rd15db576cb5b4c33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内外盘曲线" sheetId="3" r:id="R5319507f9c6c4c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗筹明细" sheetId="4" r:id="R0e2c89e81b7e455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数与来源" sheetId="5" r:id="R65d0f1aaffda4dd3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -474,7 +474,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="434">
+  <x:cellXfs count="436">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1637,6 +1637,8 @@
     <x:xf numFmtId="200" fontId="20" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="208" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="210" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1915,7 +1917,7 @@
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="C3" s="124" t="str">
-        <x:v>黄色格可编辑。预留按 10,000 USDT ÷ BNC4 价格向上取整；未填价格时建议总资金留空。Gas 单独以 BNB 计价。</x:v>
+        <x:v>黄色格可编辑。手动价格留空用指定池每日价；预留按 10,000 USDT ÷ 有效价格向上取整。Gas 单独以 BNB 计价。</x:v>
       </x:c>
       <x:c r="D3" s="124"/>
       <x:c r="E3" s="124"/>
@@ -2050,8 +2052,9 @@
       <x:c r="G8" s="130" t="str">
         <x:v>资金预留 / BNC4</x:v>
       </x:c>
-      <x:c r="H8" s="432" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),ROUNDUP('参数与来源'!$N$11/$L$14,0),"")</x:f>
+      <x:c r="H8" s="432" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),ROUNDUP('参数与来源'!$N$11/'参数与来源'!$N$19,0),"")</x:f>
+        <x:v>1734</x:v>
       </x:c>
       <x:c r="I8" s="130" t="str">
         <x:v>额外内盘资金</x:v>
@@ -2160,8 +2163,9 @@
       <x:c r="I11" s="153" t="str">
         <x:v>建议 BNC4 总资金</x:v>
       </x:c>
-      <x:c r="J11" s="433" t="str">
+      <x:c r="J11" s="433" t="n">
         <x:f>'控筹测算'!D38</x:f>
+        <x:v>11864.793859649122</x:v>
       </x:c>
       <x:c r="K11" s="130" t="str">
         <x:v>外盘成交</x:v>
@@ -2267,7 +2271,7 @@
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="K14" s="131" t="str">
-        <x:v>BNC4 / USDT 价格</x:v>
+        <x:v>手动价格 / USDT</x:v>
       </x:c>
       <x:c r="L14" s="220"/>
     </x:row>
@@ -2280,8 +2284,13 @@
       <x:c r="H15" s="23"/>
       <x:c r="I15" s="23"/>
       <x:c r="J15" s="23"/>
-      <x:c r="K15" s="23"/>
-      <x:c r="L15" s="23"/>
+      <x:c r="K15" s="23" t="str">
+        <x:v>有效价格 / USDT</x:v>
+      </x:c>
+      <x:c r="L15" s="435" t="n">
+        <x:f>'参数与来源'!$N$19</x:f>
+        <x:v>5.7682</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="C16" s="23"/>
@@ -2364,15 +2373,17 @@
         <x:f>E19/D19</x:f>
         <x:v>6.377551026340002e-7</x:v>
       </x:c>
-      <x:c r="H19" s="275" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G19))),"",G19*$L$14)</x:f>
+      <x:c r="H19" s="275" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G19))),"",G19*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00000367869898301344</x:v>
       </x:c>
       <x:c r="I19" s="279" t="n">
         <x:f>G19*'参数与来源'!$D$8</x:f>
         <x:v>637.7551026340002</x:v>
       </x:c>
-      <x:c r="J19" s="279" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I19*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J19" s="279" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I19*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>3675.623590663641</x:v>
       </x:c>
       <x:c r="K19" s="279" t="n">
         <x:f>0</x:f>
@@ -2407,15 +2418,17 @@
         <x:f>E20/D20</x:f>
         <x:v>7.754376186933351e-7</x:v>
       </x:c>
-      <x:c r="H20" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G20))),"",G20*$L$14)</x:f>
+      <x:c r="H20" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G20))),"",G20*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000004472879272146896</x:v>
       </x:c>
       <x:c r="I20" s="298" t="n">
         <x:f>G20*'参数与来源'!$D$8</x:f>
         <x:v>775.4376186933351</x:v>
       </x:c>
-      <x:c r="J20" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I20*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J20" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I20*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>4469.139945075382</x:v>
       </x:c>
       <x:c r="K20" s="298" t="n">
         <x:f>E20-E19</x:f>
@@ -2450,15 +2463,17 @@
         <x:f>E21/D21</x:f>
         <x:v>9.630408519262684e-7</x:v>
       </x:c>
-      <x:c r="H21" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G21))),"",G21*$L$14)</x:f>
+      <x:c r="H21" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G21))),"",G21*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000005555012242081102</x:v>
       </x:c>
       <x:c r="I21" s="298" t="n">
         <x:f>G21*'参数与来源'!$D$8</x:f>
         <x:v>963.0408519262684</x:v>
       </x:c>
-      <x:c r="J21" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I21*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J21" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I21*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>5550.368251846722</x:v>
       </x:c>
       <x:c r="K21" s="298" t="n">
         <x:f>E21-E20</x:f>
@@ -2493,15 +2508,17 @@
         <x:f>E22/D22</x:f>
         <x:v>0.000001227974001557687</x:v>
       </x:c>
-      <x:c r="H22" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G22))),"",G22*$L$14)</x:f>
+      <x:c r="H22" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G22))),"",G22*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000007083199635785051</x:v>
       </x:c>
       <x:c r="I22" s="298" t="n">
         <x:f>G22*'参数与来源'!$D$8</x:f>
         <x:v>1227.9740015576872</x:v>
       </x:c>
-      <x:c r="J22" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I22*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J22" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I22*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>7077.278080889535</x:v>
       </x:c>
       <x:c r="K22" s="298" t="n">
         <x:f>E22-E21</x:f>
@@ -2536,15 +2553,17 @@
         <x:f>E23/D23</x:f>
         <x:v>0.0000016194064412609305</x:v>
       </x:c>
-      <x:c r="H23" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G23))),"",G23*$L$14)</x:f>
+      <x:c r="H23" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G23))),"",G23*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0000093410602344813</x:v>
       </x:c>
       <x:c r="I23" s="298" t="n">
         <x:f>G23*'参数与来源'!$D$8</x:f>
         <x:v>1619.4064412609305</x:v>
       </x:c>
-      <x:c r="J23" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I23*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J23" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I23*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>9333.251108125274</x:v>
       </x:c>
       <x:c r="K23" s="298" t="n">
         <x:f>E23-E22</x:f>
@@ -2579,15 +2598,17 @@
         <x:f>E24/D24</x:f>
         <x:v>0.000002232842151729785</x:v>
       </x:c>
-      <x:c r="H24" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G24))),"",G24*$L$14)</x:f>
+      <x:c r="H24" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G24))),"",G24*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000012879480099607747</x:v>
       </x:c>
       <x:c r="I24" s="298" t="n">
         <x:f>G24*'参数与来源'!$D$8</x:f>
         <x:v>2232.842151729785</x:v>
       </x:c>
-      <x:c r="J24" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I24*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J24" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I24*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>12868.712854244477</x:v>
       </x:c>
       <x:c r="K24" s="298" t="n">
         <x:f>E24-E23</x:f>
@@ -2622,15 +2643,17 @@
         <x:f>E25/D25</x:f>
         <x:v>0.0000032744161289026152</x:v>
       </x:c>
-      <x:c r="H25" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G25))),"",G25*$L$14)</x:f>
+      <x:c r="H25" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G25))),"",G25*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000018887487114736067</x:v>
       </x:c>
       <x:c r="I25" s="298" t="n">
         <x:f>G25*'参数与来源'!$D$8</x:f>
         <x:v>3274.416128902615</x:v>
       </x:c>
-      <x:c r="J25" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I25*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J25" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I25*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>18871.697175508147</x:v>
       </x:c>
       <x:c r="K25" s="298" t="n">
         <x:f>E25-E24</x:f>
@@ -2665,15 +2688,17 @@
         <x:f>E26/D26</x:f>
         <x:v>0.000005259697590596034</x:v>
       </x:c>
-      <x:c r="H26" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G26))),"",G26*$L$14)</x:f>
+      <x:c r="H26" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G26))),"",G26*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000030338987642076043</x:v>
       </x:c>
       <x:c r="I26" s="298" t="n">
         <x:f>G26*'参数与来源'!$D$8</x:f>
         <x:v>5259.697590596034</x:v>
       </x:c>
-      <x:c r="J26" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I26*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J26" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I26*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>30313.624248407275</x:v>
       </x:c>
       <x:c r="K26" s="298" t="n">
         <x:f>E26-E25</x:f>
@@ -2708,15 +2733,17 @@
         <x:f>E27/D27</x:f>
         <x:v>0.000009800000062347276</x:v>
       </x:c>
-      <x:c r="H27" s="307" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G27))),"",G27*$L$14)</x:f>
+      <x:c r="H27" s="307" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G27))),"",G27*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00005652836035963156</x:v>
       </x:c>
       <x:c r="I27" s="311" t="n">
         <x:f>G27*'参数与来源'!$D$8</x:f>
         <x:v>9800.000062347275</x:v>
       </x:c>
-      <x:c r="J27" s="311" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I27*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J27" s="311" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I27*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>56481.1026503709</x:v>
       </x:c>
       <x:c r="K27" s="311" t="n">
         <x:f>E27-E26</x:f>
@@ -2824,15 +2851,17 @@
         <x:f>IF(D32="","",E32/D32)</x:f>
         <x:v>0.0000098</x:v>
       </x:c>
-      <x:c r="H32" s="320" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G32))),"",G32*$L$14)</x:f>
+      <x:c r="H32" s="320" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G32))),"",G32*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000056528359999999996</x:v>
       </x:c>
       <x:c r="I32" s="324" t="n">
         <x:f>IF(G32="","",G32*'参数与来源'!$D$8)</x:f>
         <x:v>9800</x:v>
       </x:c>
-      <x:c r="J32" s="324" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I32=""),"",I32*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J32" s="324" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I32=""),"",I32*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>56481.102291040006</x:v>
       </x:c>
       <x:c r="K32" s="324" t="n">
         <x:f>IF(E32="","",(E32-$F$8)/(1-$F$11))</x:f>
@@ -2867,15 +2896,17 @@
         <x:f>IF(D33="","",E33/D33)</x:f>
         <x:v>0.000010894163516068056</x:v>
       </x:c>
-      <x:c r="H33" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G33))),"",G33*$L$14)</x:f>
+      <x:c r="H33" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G33))),"",G33*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00006283971399338376</x:v>
       </x:c>
       <x:c r="I33" s="298" t="n">
         <x:f>IF(G33="","",G33*'参数与来源'!$D$8)</x:f>
         <x:v>10894.163516068056</x:v>
       </x:c>
-      <x:c r="J33" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I33=""),"",I33*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J33" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I33=""),"",I33*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>62787.1799924853</x:v>
       </x:c>
       <x:c r="K33" s="298" t="n">
         <x:f>IF(E33="","",(E33-$F$8)/(1-$F$11))</x:f>
@@ -2910,15 +2941,17 @@
         <x:f>IF(D34="","",E34/D34)</x:f>
         <x:v>0.000012182349055357363</x:v>
       </x:c>
-      <x:c r="H34" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G34))),"",G34*$L$14)</x:f>
+      <x:c r="H34" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G34))),"",G34*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00007027022582111234</x:v>
       </x:c>
       <x:c r="I34" s="298" t="n">
         <x:f>IF(G34="","",G34*'参数与来源'!$D$8)</x:f>
         <x:v>12182.349055357363</x:v>
       </x:c>
-      <x:c r="J34" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I34=""),"",I34*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J34" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I34=""),"",I34*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>70211.4799123259</x:v>
       </x:c>
       <x:c r="K34" s="298" t="n">
         <x:f>IF(E34="","",(E34-$F$8)/(1-$F$11))</x:f>
@@ -2953,15 +2986,17 @@
         <x:f>IF(D35="","",E35/D35)</x:f>
         <x:v>0.000013713295657346803</x:v>
       </x:c>
-      <x:c r="H35" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G35))),"",G35*$L$14)</x:f>
+      <x:c r="H35" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G35))),"",G35*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00007910103201070783</x:v>
       </x:c>
       <x:c r="I35" s="298" t="n">
         <x:f>IF(G35="","",G35*'参数与来源'!$D$8)</x:f>
         <x:v>13713.295657346802</x:v>
       </x:c>
-      <x:c r="J35" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I35=""),"",I35*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J35" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I35=""),"",I35*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>79034.90354794689</x:v>
       </x:c>
       <x:c r="K35" s="298" t="n">
         <x:f>IF(E35="","",(E35-$F$8)/(1-$F$11))</x:f>
@@ -2996,15 +3031,17 @@
         <x:f>IF(D36="","",E36/D36)</x:f>
         <x:v>0.000015552066115702468</x:v>
       </x:c>
-      <x:c r="H36" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G36))),"",G36*$L$14)</x:f>
+      <x:c r="H36" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G36))),"",G36*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00008970742776859497</x:v>
       </x:c>
       <x:c r="I36" s="298" t="n">
         <x:f>IF(G36="","",G36*'参数与来源'!$D$8)</x:f>
         <x:v>15552.066115702468</x:v>
       </x:c>
-      <x:c r="J36" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I36=""),"",I36*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J36" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I36=""),"",I36*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>89632.43235898044</x:v>
       </x:c>
       <x:c r="K36" s="298" t="n">
         <x:f>IF(E36="","",(E36-$F$8)/(1-$F$11))</x:f>
@@ -3039,15 +3076,17 @@
         <x:f>IF(D37="","",E37/D37)</x:f>
         <x:v>0.000017787075617283933</x:v>
       </x:c>
-      <x:c r="H37" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G37))),"",G37*$L$14)</x:f>
+      <x:c r="H37" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G37))),"",G37*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0001025994095756172</x:v>
       </x:c>
       <x:c r="I37" s="298" t="n">
         <x:f>IF(G37="","",G37*'参数与来源'!$D$8)</x:f>
         <x:v>17787.075617283932</x:v>
       </x:c>
-      <x:c r="J37" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I37=""),"",I37*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J37" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I37=""),"",I37*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>102513.63646921197</x:v>
       </x:c>
       <x:c r="K37" s="298" t="n">
         <x:f>IF(E37="","",(E37-$F$8)/(1-$F$11))</x:f>
@@ -3082,15 +3121,17 @@
         <x:f>IF(D38="","",E38/D38)</x:f>
         <x:v>0.00002054092225439963</x:v>
       </x:c>
-      <x:c r="H38" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G38))),"",G38*$L$14)</x:f>
+      <x:c r="H38" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G38))),"",G38*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00011848414774782794</x:v>
       </x:c>
       <x:c r="I38" s="298" t="n">
         <x:f>IF(G38="","",G38*'参数与来源'!$D$8)</x:f>
         <x:v>20540.92225439963</x:v>
       </x:c>
-      <x:c r="J38" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I38=""),"",I38*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J38" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I38=""),"",I38*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>118385.09500031076</x:v>
       </x:c>
       <x:c r="K38" s="298" t="n">
         <x:f>IF(E38="","",(E38-$F$8)/(1-$F$11))</x:f>
@@ -3125,15 +3166,17 @@
         <x:f>IF(D39="","",E39/D39)</x:f>
         <x:v>0.000023987565036420375</x:v>
       </x:c>
-      <x:c r="H39" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G39))),"",G39*$L$14)</x:f>
+      <x:c r="H39" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G39))),"",G39*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00013836507264308002</x:v>
       </x:c>
       <x:c r="I39" s="298" t="n">
         <x:f>IF(G39="","",G39*'参数与来源'!$D$8)</x:f>
         <x:v>23987.565036420376</x:v>
       </x:c>
-      <x:c r="J39" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I39=""),"",I39*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J39" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I39=""),"",I39*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>138249.39944235043</x:v>
       </x:c>
       <x:c r="K39" s="298" t="n">
         <x:f>IF(E39="","",(E39-$F$8)/(1-$F$11))</x:f>
@@ -3168,15 +3211,17 @@
         <x:f>IF(D40="","",E40/D40)</x:f>
         <x:v>0.000028380486303477972</x:v>
       </x:c>
-      <x:c r="H40" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G40))),"",G40*$L$14)</x:f>
+      <x:c r="H40" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G40))),"",G40*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00016370432109572163</x:v>
       </x:c>
       <x:c r="I40" s="298" t="n">
         <x:f>IF(G40="","",G40*'参数与来源'!$D$8)</x:f>
         <x:v>28380.48630347797</x:v>
       </x:c>
-      <x:c r="J40" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I40=""),"",I40*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J40" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I40=""),"",I40*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>163567.4642832856</x:v>
       </x:c>
       <x:c r="K40" s="298" t="n">
         <x:f>IF(E40="","",(E40-$F$8)/(1-$F$11))</x:f>
@@ -3211,15 +3256,17 @@
         <x:f>IF(D41="","",E41/D41)</x:f>
         <x:v>0.00003410066568047335</x:v>
       </x:c>
-      <x:c r="H41" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G41))),"",G41*$L$14)</x:f>
+      <x:c r="H41" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G41))),"",G41*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0001966994597781064</x:v>
       </x:c>
       <x:c r="I41" s="298" t="n">
         <x:f>IF(G41="","",G41*'参数与来源'!$D$8)</x:f>
         <x:v>34100.66568047335</x:v>
       </x:c>
-      <x:c r="J41" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I41=""),"",I41*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J41" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I41=""),"",I41*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>196535.01902973192</x:v>
       </x:c>
       <x:c r="K41" s="298" t="n">
         <x:f>IF(E41="","",(E41-$F$8)/(1-$F$11))</x:f>
@@ -3254,15 +3301,17 @@
         <x:f>IF(D42="","",E42/D42)</x:f>
         <x:v>0.00004174205522861022</x:v>
       </x:c>
-      <x:c r="H42" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G42))),"",G42*$L$14)</x:f>
+      <x:c r="H42" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G42))),"",G42*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00024077652296966947</x:v>
       </x:c>
       <x:c r="I42" s="298" t="n">
         <x:f>IF(G42="","",G42*'参数与来源'!$D$8)</x:f>
         <x:v>41742.05522861022</x:v>
       </x:c>
-      <x:c r="J42" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I42=""),"",I42*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J42" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I42=""),"",I42*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>240575.23379646684</x:v>
       </x:c>
       <x:c r="K42" s="298" t="n">
         <x:f>IF(E42="","",(E42-$F$8)/(1-$F$11))</x:f>
@@ -3297,15 +3346,17 @@
         <x:f>IF(D43="","",E43/D43)</x:f>
         <x:v>0.00005227222222222221</x:v>
       </x:c>
-      <x:c r="H43" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G43))),"",G43*$L$14)</x:f>
+      <x:c r="H43" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G43))),"",G43*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00030151663222222216</x:v>
       </x:c>
       <x:c r="I43" s="298" t="n">
         <x:f>IF(G43="","",G43*'参数与来源'!$D$8)</x:f>
         <x:v>52272.22222222221</x:v>
       </x:c>
-      <x:c r="J43" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I43=""),"",I43*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J43" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I43=""),"",I43*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>301264.5643176844</x:v>
       </x:c>
       <x:c r="K43" s="298" t="n">
         <x:f>IF(E43="","",(E43-$F$8)/(1-$F$11))</x:f>
@@ -3340,15 +3391,17 @@
         <x:f>IF(D44="","",E44/D44)</x:f>
         <x:v>0.000067354419284149</x:v>
       </x:c>
-      <x:c r="H44" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G44))),"",G44*$L$14)</x:f>
+      <x:c r="H44" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G44))),"",G44*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0003885137613148283</x:v>
       </x:c>
       <x:c r="I44" s="298" t="n">
         <x:f>IF(G44="","",G44*'参数与来源'!$D$8)</x:f>
         <x:v>67354.419284149</x:v>
       </x:c>
-      <x:c r="J44" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I44=""),"",I44*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J44" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I44=""),"",I44*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>388188.96381036914</x:v>
       </x:c>
       <x:c r="K44" s="298" t="n">
         <x:f>IF(E44="","",(E44-$F$8)/(1-$F$11))</x:f>
@@ -3383,15 +3436,17 @@
         <x:f>IF(D45="","",E45/D45)</x:f>
         <x:v>0.0000900470703125</x:v>
       </x:c>
-      <x:c r="H45" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G45))),"",G45*$L$14)</x:f>
+      <x:c r="H45" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G45))),"",G45*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0005194095109765626</x:v>
       </x:c>
       <x:c r="I45" s="298" t="n">
         <x:f>IF(G45="","",G45*'参数与来源'!$D$8)</x:f>
         <x:v>90047.0703125</x:v>
       </x:c>
-      <x:c r="J45" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I45=""),"",I45*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J45" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I45=""),"",I45*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>518975.2846253861</x:v>
       </x:c>
       <x:c r="K45" s="298" t="n">
         <x:f>IF(E45="","",(E45-$F$8)/(1-$F$11))</x:f>
@@ -3426,15 +3481,17 @@
         <x:f>IF(D46="","",E46/D46)</x:f>
         <x:v>0.000126485871056241</x:v>
       </x:c>
-      <x:c r="H46" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G46))),"",G46*$L$14)</x:f>
+      <x:c r="H46" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G46))),"",G46*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0007295958014266093</x:v>
       </x:c>
       <x:c r="I46" s="298" t="n">
         <x:f>IF(G46="","",G46*'参数与来源'!$D$8)</x:f>
         <x:v>126485.871056241</x:v>
       </x:c>
-      <x:c r="J46" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I46=""),"",I46*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J46" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I46=""),"",I46*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>728985.8593366168</x:v>
       </x:c>
       <x:c r="K46" s="298" t="n">
         <x:f>IF(E46="","",(E46-$F$8)/(1-$F$11))</x:f>
@@ -3469,15 +3526,17 @@
         <x:f>IF(D47="","",E47/D47)</x:f>
         <x:v>0.00019051280991735475</x:v>
       </x:c>
-      <x:c r="H47" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G47))),"",G47*$L$14)</x:f>
+      <x:c r="H47" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G47))),"",G47*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0010989159901652857</x:v>
       </x:c>
       <x:c r="I47" s="298" t="n">
         <x:f>IF(G47="","",G47*'参数与来源'!$D$8)</x:f>
         <x:v>190512.80991735475</x:v>
       </x:c>
-      <x:c r="J47" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I47=""),"",I47*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J47" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I47=""),"",I47*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>1097997.2963975077</x:v>
       </x:c>
       <x:c r="K47" s="298" t="n">
         <x:f>IF(E47="","",(E47-$F$8)/(1-$F$11))</x:f>
@@ -3512,15 +3571,17 @@
         <x:f>IF(D48="","",E48/D48)</x:f>
         <x:v>0.00031905951557093274</x:v>
       </x:c>
-      <x:c r="H48" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G48))),"",G48*$L$14)</x:f>
+      <x:c r="H48" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G48))),"",G48*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0018403990977162543</x:v>
       </x:c>
       <x:c r="I48" s="298" t="n">
         <x:f>IF(G48="","",G48*'参数与来源'!$D$8)</x:f>
         <x:v>319059.51557093277</x:v>
       </x:c>
-      <x:c r="J48" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I48=""),"",I48*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J48" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I48=""),"",I48*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>1838860.5240705637</x:v>
       </x:c>
       <x:c r="K48" s="298" t="n">
         <x:f>IF(E48="","",(E48-$F$8)/(1-$F$11))</x:f>
@@ -3555,15 +3616,17 @@
         <x:f>IF(D49="","",E49/D49)</x:f>
         <x:v>0.000640334722222219</x:v>
       </x:c>
-      <x:c r="H49" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G49))),"",G49*$L$14)</x:f>
+      <x:c r="H49" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G49))),"",G49*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0036935787447222035</x:v>
       </x:c>
       <x:c r="I49" s="298" t="n">
         <x:f>IF(G49="","",G49*'参数与来源'!$D$8)</x:f>
         <x:v>640334.722222219</x:v>
       </x:c>
-      <x:c r="J49" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I49=""),"",I49*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J49" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I49=""),"",I49*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>3690490.912891616</x:v>
       </x:c>
       <x:c r="K49" s="298" t="n">
         <x:f>IF(E49="","",(E49-$F$8)/(1-$F$11))</x:f>
@@ -3598,15 +3661,17 @@
         <x:f>IF(D50="","",E50/D50)</x:f>
         <x:v>0.0018817999999999814</x:v>
       </x:c>
-      <x:c r="H50" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G50))),"",G50*$L$14)</x:f>
+      <x:c r="H50" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G50))),"",G50*'参数与来源'!$N$19)</x:f>
+        <x:v>0.010854598759999893</x:v>
       </x:c>
       <x:c r="I50" s="298" t="n">
         <x:f>IF(G50="","",G50*'参数与来源'!$D$8)</x:f>
         <x:v>1881799.9999999814</x:v>
       </x:c>
-      <x:c r="J50" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I50=""),"",I50*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J50" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I50=""),"",I50*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>10845524.315436535</x:v>
       </x:c>
       <x:c r="K50" s="298" t="n">
         <x:f>IF(E50="","",(E50-$F$8)/(1-$F$11))</x:f>
@@ -3641,15 +3706,17 @@
         <x:f>IF(D51="","",E51/D51)</x:f>
         <x:v>0.0036883279999999634</x:v>
       </x:c>
-      <x:c r="H51" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G51))),"",G51*$L$14)</x:f>
+      <x:c r="H51" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G51))),"",G51*'参数与来源'!$N$19)</x:f>
+        <x:v>0.02127501356959979</x:v>
       </x:c>
       <x:c r="I51" s="298" t="n">
         <x:f>IF(G51="","",G51*'参数与来源'!$D$8)</x:f>
         <x:v>3688327.999999963</x:v>
       </x:c>
-      <x:c r="J51" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I51=""),"",I51*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J51" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I51=""),"",I51*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>21257227.658255603</x:v>
       </x:c>
       <x:c r="K51" s="298" t="n">
         <x:f>IF(E51="","",(E51-$F$8)/(1-$F$11))</x:f>
@@ -3684,15 +3751,17 @@
         <x:f>IF(D52="","",E52/D52)</x:f>
         <x:v>0.023052049999999442</x:v>
       </x:c>
-      <x:c r="H52" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G52))),"",G52*$L$14)</x:f>
+      <x:c r="H52" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G52))),"",G52*'参数与来源'!$N$19)</x:f>
+        <x:v>0.1329688348099968</x:v>
       </x:c>
       <x:c r="I52" s="298" t="n">
         <x:f>IF(G52="","",G52*'参数与来源'!$D$8)</x:f>
         <x:v>23052049.99999944</x:v>
       </x:c>
-      <x:c r="J52" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I52=""),"",I52*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J52" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I52=""),"",I52*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>132857672.86409563</x:v>
       </x:c>
       <x:c r="K52" s="298" t="n">
         <x:f>IF(E52="","",(E52-$F$8)/(1-$F$11))</x:f>
@@ -3727,15 +3796,17 @@
         <x:f>IF(D53="","",E53/D53)</x:f>
         <x:v>0.36883279999996443</x:v>
       </x:c>
-      <x:c r="H53" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G53))),"",G53*$L$14)</x:f>
+      <x:c r="H53" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G53))),"",G53*'参数与来源'!$N$19)</x:f>
+        <x:v>2.127501356959795</x:v>
       </x:c>
       <x:c r="I53" s="298" t="n">
         <x:f>IF(G53="","",G53*'参数与来源'!$D$8)</x:f>
         <x:v>368832799.9999644</x:v>
       </x:c>
-      <x:c r="J53" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I53=""),"",I53*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J53" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I53=""),"",I53*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>2125722765.8253765</x:v>
       </x:c>
       <x:c r="K53" s="298" t="n">
         <x:f>IF(E53="","",(E53-$F$8)/(1-$F$11))</x:f>
@@ -3768,13 +3839,14 @@
         <x:f>IF(D54="","",E54/D54)</x:f>
       </x:c>
       <x:c r="H54" s="344" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G54))),"",G54*$L$14)</x:f>
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G54))),"",G54*'参数与来源'!$N$19)</x:f>
       </x:c>
       <x:c r="I54" s="348" t="str">
         <x:f>IF(G54="","",G54*'参数与来源'!$D$8)</x:f>
       </x:c>
-      <x:c r="J54" s="348" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF(OR($L$14="",I54=""),"",I54*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J54" s="348" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I54=""),"",I54*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K54" s="348" t="str">
         <x:f>IF(E54="","",(E54-$F$8)/(1-$F$11))</x:f>
@@ -3880,15 +3952,17 @@
         <x:f>E59/D59</x:f>
         <x:v>0.0000098</x:v>
       </x:c>
-      <x:c r="H59" s="275" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G59))),"",G59*$L$14)</x:f>
+      <x:c r="H59" s="275" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G59))),"",G59*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000056528359999999996</x:v>
       </x:c>
       <x:c r="I59" s="279" t="n">
         <x:f>G59*'参数与来源'!$D$8</x:f>
         <x:v>9800</x:v>
       </x:c>
-      <x:c r="J59" s="279" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I59*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J59" s="279" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I59*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>56481.102291040006</x:v>
       </x:c>
       <x:c r="K59" s="363" t="n">
         <x:f>1-G59/$F$14</x:f>
@@ -3923,15 +3997,17 @@
         <x:f>E60/D60</x:f>
         <x:v>0.0000044476224522221675</x:v>
       </x:c>
-      <x:c r="H60" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G60))),"",G60*$L$14)</x:f>
+      <x:c r="H60" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G60))),"",G60*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000025654775828907908</x:v>
       </x:c>
       <x:c r="I60" s="298" t="n">
         <x:f>G60*'参数与来源'!$D$8</x:f>
         <x:v>4447.622452222167</x:v>
       </x:c>
-      <x:c r="J60" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I60*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J60" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I60*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>25633.32843631494</x:v>
       </x:c>
       <x:c r="K60" s="367" t="n">
         <x:f>1-G60/$F$14</x:f>
@@ -3966,15 +4042,17 @@
         <x:f>E61/D61</x:f>
         <x:v>0.0000025282997036149077</x:v>
       </x:c>
-      <x:c r="H61" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G61))),"",G61*$L$14)</x:f>
+      <x:c r="H61" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G61))),"",G61*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00001458373835039151</x:v>
       </x:c>
       <x:c r="I61" s="298" t="n">
         <x:f>G61*'参数与来源'!$D$8</x:f>
         <x:v>2528.2997036149077</x:v>
       </x:c>
-      <x:c r="J61" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I61*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J61" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I61*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>14571.546345130586</x:v>
       </x:c>
       <x:c r="K61" s="367" t="n">
         <x:f>1-G61/$F$14</x:f>
@@ -4009,15 +4087,17 @@
         <x:f>E62/D62</x:f>
         <x:v>0.0000016284223000428526</x:v>
       </x:c>
-      <x:c r="H62" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G62))),"",G62*$L$14)</x:f>
+      <x:c r="H62" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G62))),"",G62*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000009393065511107183</x:v>
       </x:c>
       <x:c r="I62" s="298" t="n">
         <x:f>G62*'参数与来源'!$D$8</x:f>
         <x:v>1628.4223000428526</x:v>
       </x:c>
-      <x:c r="J62" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I62*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J62" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I62*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>9385.212908339898</x:v>
       </x:c>
       <x:c r="K62" s="367" t="n">
         <x:f>1-G62/$F$14</x:f>
@@ -4052,15 +4132,17 @@
         <x:f>E63/D63</x:f>
         <x:v>0.000001135660301290678</x:v>
       </x:c>
-      <x:c r="H63" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G63))),"",G63*$L$14)</x:f>
+      <x:c r="H63" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G63))),"",G63*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00000655071574990489</x:v>
       </x:c>
       <x:c r="I63" s="298" t="n">
         <x:f>G63*'参数与来源'!$D$8</x:f>
         <x:v>1135.660301290678</x:v>
       </x:c>
-      <x:c r="J63" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I63*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J63" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I63*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>6545.239351537969</x:v>
       </x:c>
       <x:c r="K63" s="367" t="n">
         <x:f>1-G63/$F$14</x:f>
@@ -4095,15 +4177,17 @@
         <x:f>E64/D64</x:f>
         <x:v>8.369014843392542e-7</x:v>
       </x:c>
-      <x:c r="H64" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G64))),"",G64*$L$14)</x:f>
+      <x:c r="H64" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G64))),"",G64*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0000048274151419656865</x:v>
       </x:c>
       <x:c r="I64" s="298" t="n">
         <x:f>G64*'参数与来源'!$D$8</x:f>
         <x:v>836.9014843392542</x:v>
       </x:c>
-      <x:c r="J64" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I64*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J64" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I64*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>4823.379422907004</x:v>
       </x:c>
       <x:c r="K64" s="367" t="n">
         <x:f>1-G64/$F$14</x:f>
@@ -4138,15 +4222,17 @@
         <x:f>E65/D65</x:f>
         <x:v>6.422163646919991e-7</x:v>
       </x:c>
-      <x:c r="H65" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G65))),"",G65*$L$14)</x:f>
+      <x:c r="H65" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G65))),"",G65*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000003704432434816389</x:v>
       </x:c>
       <x:c r="I65" s="298" t="n">
         <x:f>G65*'参数与来源'!$D$8</x:f>
         <x:v>642.216364691999</x:v>
       </x:c>
-      <x:c r="J65" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I65*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J65" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I65*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>3701.3355293008826</x:v>
       </x:c>
       <x:c r="K65" s="367" t="n">
         <x:f>1-G65/$F$14</x:f>
@@ -4181,15 +4267,17 @@
         <x:f>E66/D66</x:f>
         <x:v>5.083324391318343e-7</x:v>
       </x:c>
-      <x:c r="H66" s="294" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G66))),"",G66*$L$14)</x:f>
+      <x:c r="H66" s="294" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G66))),"",G66*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0000029321631754002468</x:v>
       </x:c>
       <x:c r="I66" s="298" t="n">
         <x:f>G66*'参数与来源'!$D$8</x:f>
         <x:v>508.33243913183435</x:v>
       </x:c>
-      <x:c r="J66" s="298" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I66*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J66" s="298" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I66*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>2929.7118869856126</x:v>
       </x:c>
       <x:c r="K66" s="367" t="n">
         <x:f>1-G66/$F$14</x:f>
@@ -4224,15 +4312,17 @@
         <x:f>E67/D67</x:f>
         <x:v>4.123353225286894e-7</x:v>
       </x:c>
-      <x:c r="H67" s="344" t="str">
-        <x:f>IF(OR($L$14="",NOT(ISNUMBER(G67))),"",G67*$L$14)</x:f>
+      <x:c r="H67" s="344" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G67))),"",G67*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000002378432607409986</x:v>
       </x:c>
       <x:c r="I67" s="348" t="n">
         <x:f>G67*'参数与来源'!$D$8</x:f>
         <x:v>412.3353225286894</x:v>
       </x:c>
-      <x:c r="J67" s="348" t="str">
-        <x:f>IF(AND(ISNUMBER($L$14),$L$14&gt;0),(IF($L$14="","",I67*$L$14))*'参数与来源'!$N$8,"")</x:f>
+      <x:c r="J67" s="348" t="n">
+        <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I67*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
+        <x:v>2376.444237750192</x:v>
       </x:c>
       <x:c r="K67" s="371" t="n">
         <x:f>1-G67/$F$14</x:f>
@@ -4553,8 +4643,9 @@
       <x:c r="C17" s="76" t="str">
         <x:v>手操与预留</x:v>
       </x:c>
-      <x:c r="D17" s="84" t="str">
+      <x:c r="D17" s="84" t="n">
         <x:f>'控筹模型'!H8</x:f>
+        <x:v>1734</x:v>
       </x:c>
       <x:c r="E17" s="81" t="str">
         <x:v>BNC4</x:v>
@@ -4872,7 +4963,7 @@
       </x:c>
       <x:c r="D37" s="97" t="n">
         <x:f>MAX(0,$D$17)</x:f>
-        <x:v>0</x:v>
+        <x:v>1734</x:v>
       </x:c>
       <x:c r="E37" s="43" t="str">
         <x:v>BNC4</x:v>
@@ -4885,8 +4976,9 @@
       <x:c r="C38" s="208" t="str">
         <x:v>建议 BNC4 总资金</x:v>
       </x:c>
-      <x:c r="D38" s="209" t="str">
+      <x:c r="D38" s="209" t="n">
         <x:f>IF(AND(D26="可达",ISNUMBER(D17),D17&gt;=0),SUM(D34:D37),"")</x:f>
+        <x:v>11864.793859649122</x:v>
       </x:c>
       <x:c r="E38" s="208" t="str">
         <x:v>BNC4</x:v>
@@ -4906,7 +4998,7 @@
         <x:v>USD</x:v>
       </x:c>
       <x:c r="F39" s="94" t="str">
-        <x:v>手动 USDT 价格再换算 USD</x:v>
+        <x:v>有效 USDT 价格再换算 USD</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -5128,8 +5220,9 @@
         <x:f>IF(C7&lt;=80%,('参数与来源'!$D$11+F7)/('参数与来源'!$D$12-C7*'参数与来源'!$D$8),K7/J7)</x:f>
         <x:v>6.377551026340002e-7</x:v>
       </x:c>
-      <x:c r="O7" s="393" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N7))),"",N7*'控筹模型'!$L$14)</x:f>
+      <x:c r="O7" s="393" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N7))),"",N7*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00000367869898301344</x:v>
       </x:c>
       <x:c r="P7" s="398" t="n">
         <x:f>N7*'参数与来源'!$D$8</x:f>
@@ -5188,8 +5281,9 @@
         <x:f>IF(C8&lt;=80%,('参数与来源'!$D$11+F8)/('参数与来源'!$D$12-C8*'参数与来源'!$D$8),K8/J8)</x:f>
         <x:v>7.754376186933351e-7</x:v>
       </x:c>
-      <x:c r="O8" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N8))),"",N8*'控筹模型'!$L$14)</x:f>
+      <x:c r="O8" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N8))),"",N8*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000004472879272146896</x:v>
       </x:c>
       <x:c r="P8" s="416" t="n">
         <x:f>N8*'参数与来源'!$D$8</x:f>
@@ -5248,8 +5342,9 @@
         <x:f>IF(C9&lt;=80%,('参数与来源'!$D$11+F9)/('参数与来源'!$D$12-C9*'参数与来源'!$D$8),K9/J9)</x:f>
         <x:v>9.630408519262684e-7</x:v>
       </x:c>
-      <x:c r="O9" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N9))),"",N9*'控筹模型'!$L$14)</x:f>
+      <x:c r="O9" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N9))),"",N9*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000005555012242081102</x:v>
       </x:c>
       <x:c r="P9" s="416" t="n">
         <x:f>N9*'参数与来源'!$D$8</x:f>
@@ -5308,8 +5403,9 @@
         <x:f>IF(C10&lt;=80%,('参数与来源'!$D$11+F10)/('参数与来源'!$D$12-C10*'参数与来源'!$D$8),K10/J10)</x:f>
         <x:v>0.000001227974001557687</x:v>
       </x:c>
-      <x:c r="O10" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N10))),"",N10*'控筹模型'!$L$14)</x:f>
+      <x:c r="O10" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N10))),"",N10*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000007083199635785051</x:v>
       </x:c>
       <x:c r="P10" s="416" t="n">
         <x:f>N10*'参数与来源'!$D$8</x:f>
@@ -5368,8 +5464,9 @@
         <x:f>IF(C11&lt;=80%,('参数与来源'!$D$11+F11)/('参数与来源'!$D$12-C11*'参数与来源'!$D$8),K11/J11)</x:f>
         <x:v>0.0000016194064412609305</x:v>
       </x:c>
-      <x:c r="O11" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N11))),"",N11*'控筹模型'!$L$14)</x:f>
+      <x:c r="O11" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N11))),"",N11*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0000093410602344813</x:v>
       </x:c>
       <x:c r="P11" s="416" t="n">
         <x:f>N11*'参数与来源'!$D$8</x:f>
@@ -5428,8 +5525,9 @@
         <x:f>IF(C12&lt;=80%,('参数与来源'!$D$11+F12)/('参数与来源'!$D$12-C12*'参数与来源'!$D$8),K12/J12)</x:f>
         <x:v>0.000002232842151729785</x:v>
       </x:c>
-      <x:c r="O12" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N12))),"",N12*'控筹模型'!$L$14)</x:f>
+      <x:c r="O12" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N12))),"",N12*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000012879480099607747</x:v>
       </x:c>
       <x:c r="P12" s="416" t="n">
         <x:f>N12*'参数与来源'!$D$8</x:f>
@@ -5488,8 +5586,9 @@
         <x:f>IF(C13&lt;=80%,('参数与来源'!$D$11+F13)/('参数与来源'!$D$12-C13*'参数与来源'!$D$8),K13/J13)</x:f>
         <x:v>0.0000032744161289026136</x:v>
       </x:c>
-      <x:c r="O13" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N13))),"",N13*'控筹模型'!$L$14)</x:f>
+      <x:c r="O13" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N13))),"",N13*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000018887487114736057</x:v>
       </x:c>
       <x:c r="P13" s="416" t="n">
         <x:f>N13*'参数与来源'!$D$8</x:f>
@@ -5548,8 +5647,9 @@
         <x:f>IF(C14&lt;=80%,('参数与来源'!$D$11+F14)/('参数与来源'!$D$12-C14*'参数与来源'!$D$8),K14/J14)</x:f>
         <x:v>0.0000052596975905960306</x:v>
       </x:c>
-      <x:c r="O14" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N14))),"",N14*'控筹模型'!$L$14)</x:f>
+      <x:c r="O14" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N14))),"",N14*'参数与来源'!$N$19)</x:f>
+        <x:v>0.000030338987642076026</x:v>
       </x:c>
       <x:c r="P14" s="416" t="n">
         <x:f>N14*'参数与来源'!$D$8</x:f>
@@ -5608,8 +5708,9 @@
         <x:f>IF(C15&lt;=80%,('参数与来源'!$D$11+F15)/('参数与来源'!$D$12-C15*'参数与来源'!$D$8),K15/J15)</x:f>
         <x:v>0.000009800000062347276</x:v>
       </x:c>
-      <x:c r="O15" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N15))),"",N15*'控筹模型'!$L$14)</x:f>
+      <x:c r="O15" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N15))),"",N15*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00005652836035963156</x:v>
       </x:c>
       <x:c r="P15" s="416" t="n">
         <x:f>N15*'参数与来源'!$D$8</x:f>
@@ -5668,8 +5769,9 @@
         <x:f>IF(C16&lt;=80%,('参数与来源'!$D$11+F16)/('参数与来源'!$D$12-C16*'参数与来源'!$D$8),K16/J16)</x:f>
         <x:v>0.000010894163516068056</x:v>
       </x:c>
-      <x:c r="O16" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N16))),"",N16*'控筹模型'!$L$14)</x:f>
+      <x:c r="O16" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N16))),"",N16*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00006283971399338376</x:v>
       </x:c>
       <x:c r="P16" s="416" t="n">
         <x:f>N16*'参数与来源'!$D$8</x:f>
@@ -5728,8 +5830,9 @@
         <x:f>IF(C17&lt;=80%,('参数与来源'!$D$11+F17)/('参数与来源'!$D$12-C17*'参数与来源'!$D$8),K17/J17)</x:f>
         <x:v>0.000012182349055357363</x:v>
       </x:c>
-      <x:c r="O17" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N17))),"",N17*'控筹模型'!$L$14)</x:f>
+      <x:c r="O17" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N17))),"",N17*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00007027022582111234</x:v>
       </x:c>
       <x:c r="P17" s="416" t="n">
         <x:f>N17*'参数与来源'!$D$8</x:f>
@@ -5788,8 +5891,9 @@
         <x:f>IF(C18&lt;=80%,('参数与来源'!$D$11+F18)/('参数与来源'!$D$12-C18*'参数与来源'!$D$8),K18/J18)</x:f>
         <x:v>0.000013713295657346803</x:v>
       </x:c>
-      <x:c r="O18" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N18))),"",N18*'控筹模型'!$L$14)</x:f>
+      <x:c r="O18" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N18))),"",N18*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00007910103201070783</x:v>
       </x:c>
       <x:c r="P18" s="416" t="n">
         <x:f>N18*'参数与来源'!$D$8</x:f>
@@ -5848,8 +5952,9 @@
         <x:f>IF(C19&lt;=80%,('参数与来源'!$D$11+F19)/('参数与来源'!$D$12-C19*'参数与来源'!$D$8),K19/J19)</x:f>
         <x:v>0.000015552066115702468</x:v>
       </x:c>
-      <x:c r="O19" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N19))),"",N19*'控筹模型'!$L$14)</x:f>
+      <x:c r="O19" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N19))),"",N19*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00008970742776859497</x:v>
       </x:c>
       <x:c r="P19" s="416" t="n">
         <x:f>N19*'参数与来源'!$D$8</x:f>
@@ -5908,8 +6013,9 @@
         <x:f>IF(C20&lt;=80%,('参数与来源'!$D$11+F20)/('参数与来源'!$D$12-C20*'参数与来源'!$D$8),K20/J20)</x:f>
         <x:v>0.000017787075617283933</x:v>
       </x:c>
-      <x:c r="O20" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N20))),"",N20*'控筹模型'!$L$14)</x:f>
+      <x:c r="O20" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N20))),"",N20*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0001025994095756172</x:v>
       </x:c>
       <x:c r="P20" s="416" t="n">
         <x:f>N20*'参数与来源'!$D$8</x:f>
@@ -5968,8 +6074,9 @@
         <x:f>IF(C21&lt;=80%,('参数与来源'!$D$11+F21)/('参数与来源'!$D$12-C21*'参数与来源'!$D$8),K21/J21)</x:f>
         <x:v>0.00002054092225439963</x:v>
       </x:c>
-      <x:c r="O21" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N21))),"",N21*'控筹模型'!$L$14)</x:f>
+      <x:c r="O21" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N21))),"",N21*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00011848414774782794</x:v>
       </x:c>
       <x:c r="P21" s="416" t="n">
         <x:f>N21*'参数与来源'!$D$8</x:f>
@@ -6028,8 +6135,9 @@
         <x:f>IF(C22&lt;=80%,('参数与来源'!$D$11+F22)/('参数与来源'!$D$12-C22*'参数与来源'!$D$8),K22/J22)</x:f>
         <x:v>0.000023987565036420375</x:v>
       </x:c>
-      <x:c r="O22" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N22))),"",N22*'控筹模型'!$L$14)</x:f>
+      <x:c r="O22" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N22))),"",N22*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00013836507264308002</x:v>
       </x:c>
       <x:c r="P22" s="416" t="n">
         <x:f>N22*'参数与来源'!$D$8</x:f>
@@ -6088,8 +6196,9 @@
         <x:f>IF(C23&lt;=80%,('参数与来源'!$D$11+F23)/('参数与来源'!$D$12-C23*'参数与来源'!$D$8),K23/J23)</x:f>
         <x:v>0.000028380486303477972</x:v>
       </x:c>
-      <x:c r="O23" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N23))),"",N23*'控筹模型'!$L$14)</x:f>
+      <x:c r="O23" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N23))),"",N23*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00016370432109572163</x:v>
       </x:c>
       <x:c r="P23" s="416" t="n">
         <x:f>N23*'参数与来源'!$D$8</x:f>
@@ -6148,8 +6257,9 @@
         <x:f>IF(C24&lt;=80%,('参数与来源'!$D$11+F24)/('参数与来源'!$D$12-C24*'参数与来源'!$D$8),K24/J24)</x:f>
         <x:v>0.00003410066568047335</x:v>
       </x:c>
-      <x:c r="O24" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N24))),"",N24*'控筹模型'!$L$14)</x:f>
+      <x:c r="O24" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N24))),"",N24*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0001966994597781064</x:v>
       </x:c>
       <x:c r="P24" s="416" t="n">
         <x:f>N24*'参数与来源'!$D$8</x:f>
@@ -6208,8 +6318,9 @@
         <x:f>IF(C25&lt;=80%,('参数与来源'!$D$11+F25)/('参数与来源'!$D$12-C25*'参数与来源'!$D$8),K25/J25)</x:f>
         <x:v>0.00004174205522861022</x:v>
       </x:c>
-      <x:c r="O25" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N25))),"",N25*'控筹模型'!$L$14)</x:f>
+      <x:c r="O25" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N25))),"",N25*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00024077652296966947</x:v>
       </x:c>
       <x:c r="P25" s="416" t="n">
         <x:f>N25*'参数与来源'!$D$8</x:f>
@@ -6268,8 +6379,9 @@
         <x:f>IF(C26&lt;=80%,('参数与来源'!$D$11+F26)/('参数与来源'!$D$12-C26*'参数与来源'!$D$8),K26/J26)</x:f>
         <x:v>0.00005227222222222221</x:v>
       </x:c>
-      <x:c r="O26" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N26))),"",N26*'控筹模型'!$L$14)</x:f>
+      <x:c r="O26" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N26))),"",N26*'参数与来源'!$N$19)</x:f>
+        <x:v>0.00030151663222222216</x:v>
       </x:c>
       <x:c r="P26" s="416" t="n">
         <x:f>N26*'参数与来源'!$D$8</x:f>
@@ -6328,8 +6440,9 @@
         <x:f>IF(C27&lt;=80%,('参数与来源'!$D$11+F27)/('参数与来源'!$D$12-C27*'参数与来源'!$D$8),K27/J27)</x:f>
         <x:v>0.000067354419284149</x:v>
       </x:c>
-      <x:c r="O27" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N27))),"",N27*'控筹模型'!$L$14)</x:f>
+      <x:c r="O27" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N27))),"",N27*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0003885137613148283</x:v>
       </x:c>
       <x:c r="P27" s="416" t="n">
         <x:f>N27*'参数与来源'!$D$8</x:f>
@@ -6388,8 +6501,9 @@
         <x:f>IF(C28&lt;=80%,('参数与来源'!$D$11+F28)/('参数与来源'!$D$12-C28*'参数与来源'!$D$8),K28/J28)</x:f>
         <x:v>0.0000900470703125</x:v>
       </x:c>
-      <x:c r="O28" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N28))),"",N28*'控筹模型'!$L$14)</x:f>
+      <x:c r="O28" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N28))),"",N28*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0005194095109765626</x:v>
       </x:c>
       <x:c r="P28" s="416" t="n">
         <x:f>N28*'参数与来源'!$D$8</x:f>
@@ -6448,8 +6562,9 @@
         <x:f>IF(C29&lt;=80%,('参数与来源'!$D$11+F29)/('参数与来源'!$D$12-C29*'参数与来源'!$D$8),K29/J29)</x:f>
         <x:v>0.000126485871056241</x:v>
       </x:c>
-      <x:c r="O29" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N29))),"",N29*'控筹模型'!$L$14)</x:f>
+      <x:c r="O29" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N29))),"",N29*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0007295958014266093</x:v>
       </x:c>
       <x:c r="P29" s="416" t="n">
         <x:f>N29*'参数与来源'!$D$8</x:f>
@@ -6508,8 +6623,9 @@
         <x:f>IF(C30&lt;=80%,('参数与来源'!$D$11+F30)/('参数与来源'!$D$12-C30*'参数与来源'!$D$8),K30/J30)</x:f>
         <x:v>0.00019051280991735475</x:v>
       </x:c>
-      <x:c r="O30" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N30))),"",N30*'控筹模型'!$L$14)</x:f>
+      <x:c r="O30" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N30))),"",N30*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0010989159901652857</x:v>
       </x:c>
       <x:c r="P30" s="416" t="n">
         <x:f>N30*'参数与来源'!$D$8</x:f>
@@ -6568,8 +6684,9 @@
         <x:f>IF(C31&lt;=80%,('参数与来源'!$D$11+F31)/('参数与来源'!$D$12-C31*'参数与来源'!$D$8),K31/J31)</x:f>
         <x:v>0.00031905951557093274</x:v>
       </x:c>
-      <x:c r="O31" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N31))),"",N31*'控筹模型'!$L$14)</x:f>
+      <x:c r="O31" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N31))),"",N31*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0018403990977162543</x:v>
       </x:c>
       <x:c r="P31" s="416" t="n">
         <x:f>N31*'参数与来源'!$D$8</x:f>
@@ -6628,8 +6745,9 @@
         <x:f>IF(C32&lt;=80%,('参数与来源'!$D$11+F32)/('参数与来源'!$D$12-C32*'参数与来源'!$D$8),K32/J32)</x:f>
         <x:v>0.000640334722222219</x:v>
       </x:c>
-      <x:c r="O32" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N32))),"",N32*'控筹模型'!$L$14)</x:f>
+      <x:c r="O32" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N32))),"",N32*'参数与来源'!$N$19)</x:f>
+        <x:v>0.0036935787447222035</x:v>
       </x:c>
       <x:c r="P32" s="416" t="n">
         <x:f>N32*'参数与来源'!$D$8</x:f>
@@ -6688,8 +6806,9 @@
         <x:f>IF(C33&lt;=80%,('参数与来源'!$D$11+F33)/('参数与来源'!$D$12-C33*'参数与来源'!$D$8),K33/J33)</x:f>
         <x:v>0.0018817999999999814</x:v>
       </x:c>
-      <x:c r="O33" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N33))),"",N33*'控筹模型'!$L$14)</x:f>
+      <x:c r="O33" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N33))),"",N33*'参数与来源'!$N$19)</x:f>
+        <x:v>0.010854598759999893</x:v>
       </x:c>
       <x:c r="P33" s="416" t="n">
         <x:f>N33*'参数与来源'!$D$8</x:f>
@@ -6748,8 +6867,9 @@
         <x:f>IF(C34&lt;=80%,('参数与来源'!$D$11+F34)/('参数与来源'!$D$12-C34*'参数与来源'!$D$8),K34/J34)</x:f>
         <x:v>0.0036883279999999634</x:v>
       </x:c>
-      <x:c r="O34" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N34))),"",N34*'控筹模型'!$L$14)</x:f>
+      <x:c r="O34" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N34))),"",N34*'参数与来源'!$N$19)</x:f>
+        <x:v>0.02127501356959979</x:v>
       </x:c>
       <x:c r="P34" s="416" t="n">
         <x:f>N34*'参数与来源'!$D$8</x:f>
@@ -6808,8 +6928,9 @@
         <x:f>IF(C35&lt;=80%,('参数与来源'!$D$11+F35)/('参数与来源'!$D$12-C35*'参数与来源'!$D$8),K35/J35)</x:f>
         <x:v>0.023052049999999442</x:v>
       </x:c>
-      <x:c r="O35" s="411" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N35))),"",N35*'控筹模型'!$L$14)</x:f>
+      <x:c r="O35" s="411" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N35))),"",N35*'参数与来源'!$N$19)</x:f>
+        <x:v>0.1329688348099968</x:v>
       </x:c>
       <x:c r="P35" s="416" t="n">
         <x:f>N35*'参数与来源'!$D$8</x:f>
@@ -6868,8 +6989,9 @@
         <x:f>IF(C36&lt;=80%,('参数与来源'!$D$11+F36)/('参数与来源'!$D$12-C36*'参数与来源'!$D$8),K36/J36)</x:f>
         <x:v>0.36883279999996443</x:v>
       </x:c>
-      <x:c r="O36" s="424" t="str">
-        <x:f>IF(OR('控筹模型'!$L$14="",NOT(ISNUMBER(N36))),"",N36*'控筹模型'!$L$14)</x:f>
+      <x:c r="O36" s="424" t="n">
+        <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N36))),"",N36*'参数与来源'!$N$19)</x:f>
+        <x:v>2.127501356959795</x:v>
       </x:c>
       <x:c r="P36" s="429" t="n">
         <x:f>N36*'参数与来源'!$D$8</x:f>
@@ -7233,8 +7355,8 @@
       <x:c r="M8" t="str">
         <x:v>USDT / USD</x:v>
       </x:c>
-      <x:c r="N8" s="431" t="n">
-        <x:v>0.99913</x:v>
+      <x:c r="N8" s="431">
+        <x:v>0.999164</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="40" customHeight="1">
@@ -7266,8 +7388,10 @@
       <x:c r="M9" t="str">
         <x:v>汇率快照 / UTC</x:v>
       </x:c>
-      <x:c r="N9" t="n">
-        <x:v>46282.368501157405</x:v>
+      <x:c r="N9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-18T09:01:38.255Z</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="10" ht="40" customHeight="1">
@@ -7299,8 +7423,10 @@
       <x:c r="M10" t="str">
         <x:v>汇率来源</x:v>
       </x:c>
-      <x:c r="N10" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:v>
+      <x:c r="N10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="11" ht="40" customHeight="1">
@@ -7365,7 +7491,7 @@
       <x:c r="M12" t="str">
         <x:v>BNB / USDT</x:v>
       </x:c>
-      <x:c r="N12" t="n">
+      <x:c r="N12">
         <x:v>754.5107710045597</x:v>
       </x:c>
     </x:row>
@@ -7398,8 +7524,10 @@
       <x:c r="M13" t="str">
         <x:v>原生币价格时间 / UTC</x:v>
       </x:c>
-      <x:c r="N13" t="n">
-        <x:v>46283.376137210646</x:v>
+      <x:c r="N13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2026-09-18T09:01:38.255Z</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="14" ht="40" customHeight="1">
@@ -7431,8 +7559,10 @@
       <x:c r="M14" t="str">
         <x:v>原生币价格来源</x:v>
       </x:c>
-      <x:c r="N14" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
+      <x:c r="N14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="15" ht="40" customHeight="1">
@@ -7461,6 +7591,12 @@
       <x:c r="K15" s="69" t="str">
         <x:v>本表不抵扣可能收到的分红，按保守资金流处理</x:v>
       </x:c>
+      <x:c r="M15" t="str">
+        <x:v>BNC4 / USDT 每日价格</x:v>
+      </x:c>
+      <x:c r="N15" s="434" t="n">
+        <x:v>5.7682</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="C16" s="41" t="str">
@@ -7476,6 +7612,12 @@
       <x:c r="F16" s="44" t="str">
         <x:v>毕业价格 0.0000098 反推</x:v>
       </x:c>
+      <x:c r="M16" t="str">
+        <x:v>BNC4 价格时间 / UTC</x:v>
+      </x:c>
+      <x:c r="N16" t="n">
+        <x:v>46283.396544745374</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="C17" s="41" t="str">
@@ -7491,6 +7633,12 @@
       <x:c r="F17" s="44" t="str">
         <x:v>剩余 20%</x:v>
       </x:c>
+      <x:c r="M17" t="str">
+        <x:v>BNC4 价格来源</x:v>
+      </x:c>
+      <x:c r="N17" t="str">
+        <x:v>https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="C18" s="41" t="str">
@@ -7506,6 +7654,12 @@
       <x:c r="F18" s="44" t="str">
         <x:v>2,000 × (1 - 2%)</x:v>
       </x:c>
+      <x:c r="M18" t="str">
+        <x:v>BNC4 指定交易池</x:v>
+      </x:c>
+      <x:c r="N18" t="str">
+        <x:v>0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="C19" s="41" t="str">
@@ -7520,6 +7674,13 @@
       </x:c>
       <x:c r="F19" s="44" t="str">
         <x:v>初始 TOKEN × 初始 Quote</x:v>
+      </x:c>
+      <x:c r="M19" t="str">
+        <x:v>BNC4 有效价格 / USDT</x:v>
+      </x:c>
+      <x:c r="N19" s="434" t="n">
+        <x:f>IF(AND(ISNUMBER('控筹模型'!$L$14),'控筹模型'!$L$14&gt;0),'控筹模型'!$L$14,IF(AND(ISNUMBER($N$15),$N$15&gt;0),$N$15,""))</x:f>
+        <x:v>5.7682</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Rffe7e1a924f44acc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹测算" sheetId="2" r:id="Rd15db576cb5b4c33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内外盘曲线" sheetId="3" r:id="R5319507f9c6c4c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗筹明细" sheetId="4" r:id="R0e2c89e81b7e455c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数与来源" sheetId="5" r:id="R65d0f1aaffda4dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R328ec81a6e794482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹测算" sheetId="2" r:id="Rf163ef75fd0e425f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内外盘曲线" sheetId="3" r:id="Re18391e927804b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="洗筹明细" sheetId="4" r:id="R7f65398af3cc4597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数与来源" sheetId="5" r:id="R2e9a4f2059594bd8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2054,7 +2054,7 @@
       </x:c>
       <x:c r="H8" s="432" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),ROUNDUP('参数与来源'!$N$11/'参数与来源'!$N$19,0),"")</x:f>
-        <x:v>1734</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="I8" s="130" t="str">
         <x:v>额外内盘资金</x:v>
@@ -2165,7 +2165,7 @@
       </x:c>
       <x:c r="J11" s="433" t="n">
         <x:f>'控筹测算'!D38</x:f>
-        <x:v>11864.793859649122</x:v>
+        <x:v>11840.793859649122</x:v>
       </x:c>
       <x:c r="K11" s="130" t="str">
         <x:v>外盘成交</x:v>
@@ -2289,7 +2289,7 @@
       </x:c>
       <x:c r="L15" s="435" t="n">
         <x:f>'参数与来源'!$N$19</x:f>
-        <x:v>5.7682</x:v>
+        <x:v>5.8494</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2375,7 +2375,7 @@
       </x:c>
       <x:c r="H19" s="275" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G19))),"",G19*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00000367869898301344</x:v>
+        <x:v>0.0000037304846973473208</x:v>
       </x:c>
       <x:c r="I19" s="279" t="n">
         <x:f>G19*'参数与来源'!$D$8</x:f>
@@ -2383,7 +2383,7 @@
       </x:c>
       <x:c r="J19" s="279" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I19*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>3675.623590663641</x:v>
+        <x:v>3727.3883950485224</x:v>
       </x:c>
       <x:c r="K19" s="279" t="n">
         <x:f>0</x:f>
@@ -2420,7 +2420,7 @@
       </x:c>
       <x:c r="H20" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G20))),"",G20*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000004472879272146896</x:v>
+        <x:v>0.000004535844806784795</x:v>
       </x:c>
       <x:c r="I20" s="298" t="n">
         <x:f>G20*'参数与来源'!$D$8</x:f>
@@ -2428,7 +2428,7 @@
       </x:c>
       <x:c r="J20" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I20*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>4469.139945075382</x:v>
+        <x:v>4532.080055595164</x:v>
       </x:c>
       <x:c r="K20" s="298" t="n">
         <x:f>E20-E19</x:f>
@@ -2465,7 +2465,7 @@
       </x:c>
       <x:c r="H21" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G21))),"",G21*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000005555012242081102</x:v>
+        <x:v>0.000005633211159257515</x:v>
       </x:c>
       <x:c r="I21" s="298" t="n">
         <x:f>G21*'参数与来源'!$D$8</x:f>
@@ -2473,7 +2473,7 @@
       </x:c>
       <x:c r="J21" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I21*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>5550.368251846722</x:v>
+        <x:v>5628.535593995331</x:v>
       </x:c>
       <x:c r="K21" s="298" t="n">
         <x:f>E21-E20</x:f>
@@ -2510,7 +2510,7 @@
       </x:c>
       <x:c r="H22" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G22))),"",G22*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000007083199635785051</x:v>
+        <x:v>0.000007182911124711535</x:v>
       </x:c>
       <x:c r="I22" s="298" t="n">
         <x:f>G22*'参数与来源'!$D$8</x:f>
@@ -2518,7 +2518,7 @@
       </x:c>
       <x:c r="J22" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I22*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>7077.278080889535</x:v>
+        <x:v>7176.949308478024</x:v>
       </x:c>
       <x:c r="K22" s="298" t="n">
         <x:f>E22-E21</x:f>
@@ -2555,7 +2555,7 @@
       </x:c>
       <x:c r="H23" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G23))),"",G23*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0000093410602344813</x:v>
+        <x:v>0.000009472556037511687</x:v>
       </x:c>
       <x:c r="I23" s="298" t="n">
         <x:f>G23*'参数与来源'!$D$8</x:f>
@@ -2563,7 +2563,7 @@
       </x:c>
       <x:c r="J23" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I23*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>9333.251108125274</x:v>
+        <x:v>9464.693816000552</x:v>
       </x:c>
       <x:c r="K23" s="298" t="n">
         <x:f>E23-E22</x:f>
@@ -2600,7 +2600,7 @@
       </x:c>
       <x:c r="H24" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G24))),"",G24*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000012879480099607747</x:v>
+        <x:v>0.000013060786882328206</x:v>
       </x:c>
       <x:c r="I24" s="298" t="n">
         <x:f>G24*'参数与来源'!$D$8</x:f>
@@ -2608,7 +2608,7 @@
       </x:c>
       <x:c r="J24" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I24*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>12868.712854244477</x:v>
+        <x:v>13049.946429215874</x:v>
       </x:c>
       <x:c r="K24" s="298" t="n">
         <x:f>E24-E23</x:f>
@@ -2645,7 +2645,7 @@
       </x:c>
       <x:c r="H25" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G25))),"",G25*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000018887487114736067</x:v>
+        <x:v>0.000019153369704402957</x:v>
       </x:c>
       <x:c r="I25" s="298" t="n">
         <x:f>G25*'参数与来源'!$D$8</x:f>
@@ -2653,7 +2653,7 @@
       </x:c>
       <x:c r="J25" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I25*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>18871.697175508147</x:v>
+        <x:v>19137.472407548303</x:v>
       </x:c>
       <x:c r="K25" s="298" t="n">
         <x:f>E25-E24</x:f>
@@ -2690,7 +2690,7 @@
       </x:c>
       <x:c r="H26" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G26))),"",G26*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000030338987642076043</x:v>
+        <x:v>0.00003076607508643244</x:v>
       </x:c>
       <x:c r="I26" s="298" t="n">
         <x:f>G26*'参数与来源'!$D$8</x:f>
@@ -2698,7 +2698,7 @@
       </x:c>
       <x:c r="J26" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I26*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>30313.624248407275</x:v>
+        <x:v>30740.539244110703</x:v>
       </x:c>
       <x:c r="K26" s="298" t="n">
         <x:f>E26-E25</x:f>
@@ -2735,7 +2735,7 @@
       </x:c>
       <x:c r="H27" s="307" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G27))),"",G27*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00005652836035963156</x:v>
+        <x:v>0.00005732412036469416</x:v>
       </x:c>
       <x:c r="I27" s="311" t="n">
         <x:f>G27*'参数与来源'!$D$8</x:f>
@@ -2743,7 +2743,7 @@
       </x:c>
       <x:c r="J27" s="311" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I27*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>56481.1026503709</x:v>
+        <x:v>57276.541344791454</x:v>
       </x:c>
       <x:c r="K27" s="311" t="n">
         <x:f>E27-E26</x:f>
@@ -2853,7 +2853,7 @@
       </x:c>
       <x:c r="H32" s="320" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G32))),"",G32*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000056528359999999996</x:v>
+        <x:v>0.00005732412</x:v>
       </x:c>
       <x:c r="I32" s="324" t="n">
         <x:f>IF(G32="","",G32*'参数与来源'!$D$8)</x:f>
@@ -2861,7 +2861,7 @@
       </x:c>
       <x:c r="J32" s="324" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I32=""),"",I32*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>56481.102291040006</x:v>
+        <x:v>57276.5409804</x:v>
       </x:c>
       <x:c r="K32" s="324" t="n">
         <x:f>IF(E32="","",(E32-$F$8)/(1-$F$11))</x:f>
@@ -2898,7 +2898,7 @@
       </x:c>
       <x:c r="H33" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G33))),"",G33*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00006283971399338376</x:v>
+        <x:v>0.00006372432007088848</x:v>
       </x:c>
       <x:c r="I33" s="298" t="n">
         <x:f>IF(G33="","",G33*'参数与来源'!$D$8)</x:f>
@@ -2906,7 +2906,7 @@
       </x:c>
       <x:c r="J33" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I33=""),"",I33*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>62787.1799924853</x:v>
+        <x:v>63671.42888522965</x:v>
       </x:c>
       <x:c r="K33" s="298" t="n">
         <x:f>IF(E33="","",(E33-$F$8)/(1-$F$11))</x:f>
@@ -2943,7 +2943,7 @@
       </x:c>
       <x:c r="H34" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G34))),"",G34*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00007027022582111234</x:v>
+        <x:v>0.00007125943256440737</x:v>
       </x:c>
       <x:c r="I34" s="298" t="n">
         <x:f>IF(G34="","",G34*'参数与来源'!$D$8)</x:f>
@@ -2951,7 +2951,7 @@
       </x:c>
       <x:c r="J34" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I34=""),"",I34*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>70211.4799123259</x:v>
+        <x:v>71200.2872353789</x:v>
       </x:c>
       <x:c r="K34" s="298" t="n">
         <x:f>IF(E34="","",(E34-$F$8)/(1-$F$11))</x:f>
@@ -2988,7 +2988,7 @@
       </x:c>
       <x:c r="H35" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G35))),"",G35*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00007910103201070783</x:v>
+        <x:v>0.0000802145516180844</x:v>
       </x:c>
       <x:c r="I35" s="298" t="n">
         <x:f>IF(G35="","",G35*'参数与来源'!$D$8)</x:f>
@@ -2996,7 +2996,7 @@
       </x:c>
       <x:c r="J35" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I35=""),"",I35*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>79034.90354794689</x:v>
+        <x:v>80147.97354024138</x:v>
       </x:c>
       <x:c r="K35" s="298" t="n">
         <x:f>IF(E35="","",(E35-$F$8)/(1-$F$11))</x:f>
@@ -3033,7 +3033,7 @@
       </x:c>
       <x:c r="H36" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G36))),"",G36*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00008970742776859497</x:v>
+        <x:v>0.00009097025553719002</x:v>
       </x:c>
       <x:c r="I36" s="298" t="n">
         <x:f>IF(G36="","",G36*'参数与来源'!$D$8)</x:f>
@@ -3041,7 +3041,7 @@
       </x:c>
       <x:c r="J36" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I36=""),"",I36*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>89632.43235898044</x:v>
+        <x:v>90894.75022509416</x:v>
       </x:c>
       <x:c r="K36" s="298" t="n">
         <x:f>IF(E36="","",(E36-$F$8)/(1-$F$11))</x:f>
@@ -3078,7 +3078,7 @@
       </x:c>
       <x:c r="H37" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G37))),"",G37*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0001025994095756172</x:v>
+        <x:v>0.00010404372011574064</x:v>
       </x:c>
       <x:c r="I37" s="298" t="n">
         <x:f>IF(G37="","",G37*'参数与来源'!$D$8)</x:f>
@@ -3086,7 +3086,7 @@
       </x:c>
       <x:c r="J37" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I37=""),"",I37*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>102513.63646921197</x:v>
+        <x:v>103957.36382804457</x:v>
       </x:c>
       <x:c r="K37" s="298" t="n">
         <x:f>IF(E37="","",(E37-$F$8)/(1-$F$11))</x:f>
@@ -3123,7 +3123,7 @@
       </x:c>
       <x:c r="H38" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G38))),"",G38*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00011848414774782794</x:v>
+        <x:v>0.0001201520706348852</x:v>
       </x:c>
       <x:c r="I38" s="298" t="n">
         <x:f>IF(G38="","",G38*'参数与来源'!$D$8)</x:f>
@@ -3131,7 +3131,7 @@
       </x:c>
       <x:c r="J38" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I38=""),"",I38*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>118385.09500031076</x:v>
+        <x:v>120052.34441625825</x:v>
       </x:c>
       <x:c r="K38" s="298" t="n">
         <x:f>IF(E38="","",(E38-$F$8)/(1-$F$11))</x:f>
@@ -3168,7 +3168,7 @@
       </x:c>
       <x:c r="H39" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G39))),"",G39*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00013836507264308002</x:v>
+        <x:v>0.00014031286292403734</x:v>
       </x:c>
       <x:c r="I39" s="298" t="n">
         <x:f>IF(G39="","",G39*'参数与来源'!$D$8)</x:f>
@@ -3176,7 +3176,7 @@
       </x:c>
       <x:c r="J39" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I39=""),"",I39*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>138249.39944235043</x:v>
+        <x:v>140196.4032478104</x:v>
       </x:c>
       <x:c r="K39" s="298" t="n">
         <x:f>IF(E39="","",(E39-$F$8)/(1-$F$11))</x:f>
@@ -3213,7 +3213,7 @@
       </x:c>
       <x:c r="H40" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G40))),"",G40*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00016370432109572163</x:v>
+        <x:v>0.00016600881658356405</x:v>
       </x:c>
       <x:c r="I40" s="298" t="n">
         <x:f>IF(G40="","",G40*'参数与来源'!$D$8)</x:f>
@@ -3221,7 +3221,7 @@
       </x:c>
       <x:c r="J40" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I40=""),"",I40*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>163567.4642832856</x:v>
+        <x:v>165871.02926579968</x:v>
       </x:c>
       <x:c r="K40" s="298" t="n">
         <x:f>IF(E40="","",(E40-$F$8)/(1-$F$11))</x:f>
@@ -3258,7 +3258,7 @@
       </x:c>
       <x:c r="H41" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G41))),"",G41*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0001966994597781064</x:v>
+        <x:v>0.00019946843383136082</x:v>
       </x:c>
       <x:c r="I41" s="298" t="n">
         <x:f>IF(G41="","",G41*'参数与来源'!$D$8)</x:f>
@@ -3266,7 +3266,7 @@
       </x:c>
       <x:c r="J41" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I41=""),"",I41*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>196535.01902973192</x:v>
+        <x:v>199302.8750312808</x:v>
       </x:c>
       <x:c r="K41" s="298" t="n">
         <x:f>IF(E41="","",(E41-$F$8)/(1-$F$11))</x:f>
@@ -3303,7 +3303,7 @@
       </x:c>
       <x:c r="H42" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G42))),"",G42*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00024077652296966947</x:v>
+        <x:v>0.0002441659778542326</x:v>
       </x:c>
       <x:c r="I42" s="298" t="n">
         <x:f>IF(G42="","",G42*'参数与来源'!$D$8)</x:f>
@@ -3311,7 +3311,7 @@
       </x:c>
       <x:c r="J42" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I42=""),"",I42*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>240575.23379646684</x:v>
+        <x:v>243963.3200926136</x:v>
       </x:c>
       <x:c r="K42" s="298" t="n">
         <x:f>IF(E42="","",(E42-$F$8)/(1-$F$11))</x:f>
@@ -3348,7 +3348,7 @@
       </x:c>
       <x:c r="H43" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G43))),"",G43*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00030151663222222216</x:v>
+        <x:v>0.0003057611366666666</x:v>
       </x:c>
       <x:c r="I43" s="298" t="n">
         <x:f>IF(G43="","",G43*'参数与来源'!$D$8)</x:f>
@@ -3356,7 +3356,7 @@
       </x:c>
       <x:c r="J43" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I43=""),"",I43*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>301264.5643176844</x:v>
+        <x:v>305507.3549232333</x:v>
       </x:c>
       <x:c r="K43" s="298" t="n">
         <x:f>IF(E43="","",(E43-$F$8)/(1-$F$11))</x:f>
@@ -3393,7 +3393,7 @@
       </x:c>
       <x:c r="H44" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G44))),"",G44*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0003885137613148283</x:v>
+        <x:v>0.0003939829401607012</x:v>
       </x:c>
       <x:c r="I44" s="298" t="n">
         <x:f>IF(G44="","",G44*'参数与来源'!$D$8)</x:f>
@@ -3401,7 +3401,7 @@
       </x:c>
       <x:c r="J44" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I44=""),"",I44*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>388188.96381036914</x:v>
+        <x:v>393655.9343203678</x:v>
       </x:c>
       <x:c r="K44" s="298" t="n">
         <x:f>IF(E44="","",(E44-$F$8)/(1-$F$11))</x:f>
@@ -3438,7 +3438,7 @@
       </x:c>
       <x:c r="H45" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G45))),"",G45*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0005194095109765626</x:v>
+        <x:v>0.0005267213330859376</x:v>
       </x:c>
       <x:c r="I45" s="298" t="n">
         <x:f>IF(G45="","",G45*'参数与来源'!$D$8)</x:f>
@@ -3446,7 +3446,7 @@
       </x:c>
       <x:c r="J45" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I45=""),"",I45*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>518975.2846253861</x:v>
+        <x:v>526284.1543794762</x:v>
       </x:c>
       <x:c r="K45" s="298" t="n">
         <x:f>IF(E45="","",(E45-$F$8)/(1-$F$11))</x:f>
@@ -3483,7 +3483,7 @@
       </x:c>
       <x:c r="H46" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G46))),"",G46*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0007295958014266093</x:v>
+        <x:v>0.0007398664541563761</x:v>
       </x:c>
       <x:c r="I46" s="298" t="n">
         <x:f>IF(G46="","",G46*'参数与来源'!$D$8)</x:f>
@@ -3491,7 +3491,7 @@
       </x:c>
       <x:c r="J46" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I46=""),"",I46*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>728985.8593366168</x:v>
+        <x:v>739252.3649994263</x:v>
       </x:c>
       <x:c r="K46" s="298" t="n">
         <x:f>IF(E46="","",(E46-$F$8)/(1-$F$11))</x:f>
@@ -3528,7 +3528,7 @@
       </x:c>
       <x:c r="H47" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G47))),"",G47*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0010989159901652857</x:v>
+        <x:v>0.001114385630330575</x:v>
       </x:c>
       <x:c r="I47" s="298" t="n">
         <x:f>IF(G47="","",G47*'参数与来源'!$D$8)</x:f>
@@ -3536,7 +3536,7 @@
       </x:c>
       <x:c r="J47" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I47=""),"",I47*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>1097997.2963975077</x:v>
+        <x:v>1113460.6902574005</x:v>
       </x:c>
       <x:c r="K47" s="298" t="n">
         <x:f>IF(E47="","",(E47-$F$8)/(1-$F$11))</x:f>
@@ -3573,7 +3573,7 @@
       </x:c>
       <x:c r="H48" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G48))),"",G48*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0018403990977162543</x:v>
+        <x:v>0.0018663067303806141</x:v>
       </x:c>
       <x:c r="I48" s="298" t="n">
         <x:f>IF(G48="","",G48*'参数与来源'!$D$8)</x:f>
@@ -3581,7 +3581,7 @@
       </x:c>
       <x:c r="J48" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I48=""),"",I48*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>1838860.5240705637</x:v>
+        <x:v>1864757.6957943984</x:v>
       </x:c>
       <x:c r="K48" s="298" t="n">
         <x:f>IF(E48="","",(E48-$F$8)/(1-$F$11))</x:f>
@@ -3618,7 +3618,7 @@
       </x:c>
       <x:c r="H49" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G49))),"",G49*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0036935787447222035</x:v>
+        <x:v>0.003745573924166648</x:v>
       </x:c>
       <x:c r="I49" s="298" t="n">
         <x:f>IF(G49="","",G49*'参数与来源'!$D$8)</x:f>
@@ -3626,7 +3626,7 @@
       </x:c>
       <x:c r="J49" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I49=""),"",I49*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>3690490.912891616</x:v>
+        <x:v>3742465.0978095895</x:v>
       </x:c>
       <x:c r="K49" s="298" t="n">
         <x:f>IF(E49="","",(E49-$F$8)/(1-$F$11))</x:f>
@@ -3663,7 +3663,7 @@
       </x:c>
       <x:c r="H50" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G50))),"",G50*'参数与来源'!$N$19)</x:f>
-        <x:v>0.010854598759999893</x:v>
+        <x:v>0.011007400919999891</x:v>
       </x:c>
       <x:c r="I50" s="298" t="n">
         <x:f>IF(G50="","",G50*'参数与来源'!$D$8)</x:f>
@@ -3671,7 +3671,7 @@
       </x:c>
       <x:c r="J50" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I50=""),"",I50*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>10845524.315436535</x:v>
+        <x:v>10998264.777236292</x:v>
       </x:c>
       <x:c r="K50" s="298" t="n">
         <x:f>IF(E50="","",(E50-$F$8)/(1-$F$11))</x:f>
@@ -3708,7 +3708,7 @@
       </x:c>
       <x:c r="H51" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G51))),"",G51*'参数与来源'!$N$19)</x:f>
-        <x:v>0.02127501356959979</x:v>
+        <x:v>0.021574505803199785</x:v>
       </x:c>
       <x:c r="I51" s="298" t="n">
         <x:f>IF(G51="","",G51*'参数与来源'!$D$8)</x:f>
@@ -3716,7 +3716,7 @@
       </x:c>
       <x:c r="J51" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I51=""),"",I51*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>21257227.658255603</x:v>
+        <x:v>21556598.96338313</x:v>
       </x:c>
       <x:c r="K51" s="298" t="n">
         <x:f>IF(E51="","",(E51-$F$8)/(1-$F$11))</x:f>
@@ -3753,7 +3753,7 @@
       </x:c>
       <x:c r="H52" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G52))),"",G52*'参数与来源'!$N$19)</x:f>
-        <x:v>0.1329688348099968</x:v>
+        <x:v>0.13484066126999675</x:v>
       </x:c>
       <x:c r="I52" s="298" t="n">
         <x:f>IF(G52="","",G52*'参数与来源'!$D$8)</x:f>
@@ -3761,7 +3761,7 @@
       </x:c>
       <x:c r="J52" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I52=""),"",I52*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>132857672.86409563</x:v>
+        <x:v>134728743.52114263</x:v>
       </x:c>
       <x:c r="K52" s="298" t="n">
         <x:f>IF(E52="","",(E52-$F$8)/(1-$F$11))</x:f>
@@ -3798,7 +3798,7 @@
       </x:c>
       <x:c r="H53" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G53))),"",G53*'参数与来源'!$N$19)</x:f>
-        <x:v>2.127501356959795</x:v>
+        <x:v>2.157450580319792</x:v>
       </x:c>
       <x:c r="I53" s="298" t="n">
         <x:f>IF(G53="","",G53*'参数与来源'!$D$8)</x:f>
@@ -3806,7 +3806,7 @@
       </x:c>
       <x:c r="J53" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF(OR('参数与来源'!$N$19="",I53=""),"",I53*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>2125722765.8253765</x:v>
+        <x:v>2155659896.338126</x:v>
       </x:c>
       <x:c r="K53" s="298" t="n">
         <x:f>IF(E53="","",(E53-$F$8)/(1-$F$11))</x:f>
@@ -3954,7 +3954,7 @@
       </x:c>
       <x:c r="H59" s="275" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G59))),"",G59*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000056528359999999996</x:v>
+        <x:v>0.00005732412</x:v>
       </x:c>
       <x:c r="I59" s="279" t="n">
         <x:f>G59*'参数与来源'!$D$8</x:f>
@@ -3962,7 +3962,7 @@
       </x:c>
       <x:c r="J59" s="279" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I59*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>56481.102291040006</x:v>
+        <x:v>57276.5409804</x:v>
       </x:c>
       <x:c r="K59" s="363" t="n">
         <x:f>1-G59/$F$14</x:f>
@@ -3999,7 +3999,7 @@
       </x:c>
       <x:c r="H60" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G60))),"",G60*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000025654775828907908</x:v>
+        <x:v>0.00002601592277202835</x:v>
       </x:c>
       <x:c r="I60" s="298" t="n">
         <x:f>G60*'参数与来源'!$D$8</x:f>
@@ -4007,7 +4007,7 @@
       </x:c>
       <x:c r="J60" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I60*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>25633.32843631494</x:v>
+        <x:v>25994.329556127563</x:v>
       </x:c>
       <x:c r="K60" s="367" t="n">
         <x:f>1-G60/$F$14</x:f>
@@ -4044,7 +4044,7 @@
       </x:c>
       <x:c r="H61" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G61))),"",G61*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00001458373835039151</x:v>
+        <x:v>0.000014789036286325041</x:v>
       </x:c>
       <x:c r="I61" s="298" t="n">
         <x:f>G61*'参数与来源'!$D$8</x:f>
@@ -4052,7 +4052,7 @@
       </x:c>
       <x:c r="J61" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I61*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>14571.546345130586</x:v>
+        <x:v>14776.761386207392</x:v>
       </x:c>
       <x:c r="K61" s="367" t="n">
         <x:f>1-G61/$F$14</x:f>
@@ -4089,7 +4089,7 @@
       </x:c>
       <x:c r="H62" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G62))),"",G62*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000009393065511107183</x:v>
+        <x:v>0.000009525293401870663</x:v>
       </x:c>
       <x:c r="I62" s="298" t="n">
         <x:f>G62*'参数与来源'!$D$8</x:f>
@@ -4097,7 +4097,7 @@
       </x:c>
       <x:c r="J62" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I62*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>9385.212908339898</x:v>
+        <x:v>9517.38740834711</x:v>
       </x:c>
       <x:c r="K62" s="367" t="n">
         <x:f>1-G62/$F$14</x:f>
@@ -4134,7 +4134,7 @@
       </x:c>
       <x:c r="H63" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G63))),"",G63*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00000655071574990489</x:v>
+        <x:v>0.000006642931366369693</x:v>
       </x:c>
       <x:c r="I63" s="298" t="n">
         <x:f>G63*'参数与来源'!$D$8</x:f>
@@ -4142,7 +4142,7 @@
       </x:c>
       <x:c r="J63" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I63*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>6545.239351537969</x:v>
+        <x:v>6637.417733335606</x:v>
       </x:c>
       <x:c r="K63" s="367" t="n">
         <x:f>1-G63/$F$14</x:f>
@@ -4179,7 +4179,7 @@
       </x:c>
       <x:c r="H64" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G64))),"",G64*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0000048274151419656865</x:v>
+        <x:v>0.000004895371542494034</x:v>
       </x:c>
       <x:c r="I64" s="298" t="n">
         <x:f>G64*'参数与来源'!$D$8</x:f>
@@ -4187,7 +4187,7 @@
       </x:c>
       <x:c r="J64" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I64*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>4823.379422907004</x:v>
+        <x:v>4891.308384113764</x:v>
       </x:c>
       <x:c r="K64" s="367" t="n">
         <x:f>1-G64/$F$14</x:f>
@@ -4224,7 +4224,7 @@
       </x:c>
       <x:c r="H65" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G65))),"",G65*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000003704432434816389</x:v>
+        <x:v>0.0000037565804036293793</x:v>
       </x:c>
       <x:c r="I65" s="298" t="n">
         <x:f>G65*'参数与来源'!$D$8</x:f>
@@ -4232,7 +4232,7 @@
       </x:c>
       <x:c r="J65" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I65*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>3701.3355293008826</x:v>
+        <x:v>3753.462441894367</x:v>
       </x:c>
       <x:c r="K65" s="367" t="n">
         <x:f>1-G65/$F$14</x:f>
@@ -4269,7 +4269,7 @@
       </x:c>
       <x:c r="H66" s="294" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G66))),"",G66*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0000029321631754002468</x:v>
+        <x:v>0.0000029734397694577518</x:v>
       </x:c>
       <x:c r="I66" s="298" t="n">
         <x:f>G66*'参数与来源'!$D$8</x:f>
@@ -4277,7 +4277,7 @@
       </x:c>
       <x:c r="J66" s="298" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I66*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>2929.7118869856126</x:v>
+        <x:v>2970.971814449102</x:v>
       </x:c>
       <x:c r="K66" s="367" t="n">
         <x:f>1-G66/$F$14</x:f>
@@ -4314,7 +4314,7 @@
       </x:c>
       <x:c r="H67" s="344" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(G67))),"",G67*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000002378432607409986</x:v>
+        <x:v>0.000002411914235599316</x:v>
       </x:c>
       <x:c r="I67" s="348" t="n">
         <x:f>G67*'参数与来源'!$D$8</x:f>
@@ -4322,7 +4322,7 @@
       </x:c>
       <x:c r="J67" s="348" t="n">
         <x:f>IF(AND(ISNUMBER('参数与来源'!$N$19),'参数与来源'!$N$19&gt;0),(IF('参数与来源'!$N$19="","",I67*'参数与来源'!$N$19))*'参数与来源'!$N$8,"")</x:f>
-        <x:v>2376.444237750192</x:v>
+        <x:v>2409.9123467837685</x:v>
       </x:c>
       <x:c r="K67" s="371" t="n">
         <x:f>1-G67/$F$14</x:f>
@@ -4645,7 +4645,7 @@
       </x:c>
       <x:c r="D17" s="84" t="n">
         <x:f>'控筹模型'!H8</x:f>
-        <x:v>1734</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="E17" s="81" t="str">
         <x:v>BNC4</x:v>
@@ -4674,8 +4674,9 @@
       <x:c r="C19" s="76" t="str">
         <x:v>BNC4 / USDT 价格</x:v>
       </x:c>
-      <x:c r="D19" s="84" t="str">
-        <x:f>IF('控筹模型'!L14="","",'控筹模型'!L14)</x:f>
+      <x:c r="D19" s="84" t="n">
+        <x:f>IF('参数与来源'!$N$19="","",'参数与来源'!$N$19)</x:f>
+        <x:v>5.8494</x:v>
       </x:c>
       <x:c r="E19" s="81" t="str">
         <x:v>可选；留空不输出 USD</x:v>
@@ -4963,7 +4964,7 @@
       </x:c>
       <x:c r="D37" s="97" t="n">
         <x:f>MAX(0,$D$17)</x:f>
-        <x:v>1734</x:v>
+        <x:v>1710</x:v>
       </x:c>
       <x:c r="E37" s="43" t="str">
         <x:v>BNC4</x:v>
@@ -4978,7 +4979,7 @@
       </x:c>
       <x:c r="D38" s="209" t="n">
         <x:f>IF(AND(D26="可达",ISNUMBER(D17),D17&gt;=0),SUM(D34:D37),"")</x:f>
-        <x:v>11864.793859649122</x:v>
+        <x:v>11840.793859649122</x:v>
       </x:c>
       <x:c r="E38" s="208" t="str">
         <x:v>BNC4</x:v>
@@ -4991,8 +4992,9 @@
       <x:c r="C39" s="88" t="str">
         <x:v>建议资金 / USD</x:v>
       </x:c>
-      <x:c r="D39" s="97" t="str">
+      <x:c r="D39" s="97" t="n">
         <x:f>IF(AND(ISNUMBER(D38),ISNUMBER(D19),D19&gt;0),D38*D19*'参数与来源'!$N$8,"")</x:f>
+        <x:v>69204.05252476138</x:v>
       </x:c>
       <x:c r="E39" s="43" t="str">
         <x:v>USD</x:v>
@@ -5222,7 +5224,7 @@
       </x:c>
       <x:c r="O7" s="393" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N7))),"",N7*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00000367869898301344</x:v>
+        <x:v>0.0000037304846973473208</x:v>
       </x:c>
       <x:c r="P7" s="398" t="n">
         <x:f>N7*'参数与来源'!$D$8</x:f>
@@ -5283,7 +5285,7 @@
       </x:c>
       <x:c r="O8" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N8))),"",N8*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000004472879272146896</x:v>
+        <x:v>0.000004535844806784795</x:v>
       </x:c>
       <x:c r="P8" s="416" t="n">
         <x:f>N8*'参数与来源'!$D$8</x:f>
@@ -5344,7 +5346,7 @@
       </x:c>
       <x:c r="O9" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N9))),"",N9*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000005555012242081102</x:v>
+        <x:v>0.000005633211159257515</x:v>
       </x:c>
       <x:c r="P9" s="416" t="n">
         <x:f>N9*'参数与来源'!$D$8</x:f>
@@ -5405,7 +5407,7 @@
       </x:c>
       <x:c r="O10" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N10))),"",N10*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000007083199635785051</x:v>
+        <x:v>0.000007182911124711535</x:v>
       </x:c>
       <x:c r="P10" s="416" t="n">
         <x:f>N10*'参数与来源'!$D$8</x:f>
@@ -5466,7 +5468,7 @@
       </x:c>
       <x:c r="O11" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N11))),"",N11*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0000093410602344813</x:v>
+        <x:v>0.000009472556037511687</x:v>
       </x:c>
       <x:c r="P11" s="416" t="n">
         <x:f>N11*'参数与来源'!$D$8</x:f>
@@ -5527,7 +5529,7 @@
       </x:c>
       <x:c r="O12" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N12))),"",N12*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000012879480099607747</x:v>
+        <x:v>0.000013060786882328206</x:v>
       </x:c>
       <x:c r="P12" s="416" t="n">
         <x:f>N12*'参数与来源'!$D$8</x:f>
@@ -5588,7 +5590,7 @@
       </x:c>
       <x:c r="O13" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N13))),"",N13*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000018887487114736057</x:v>
+        <x:v>0.000019153369704402947</x:v>
       </x:c>
       <x:c r="P13" s="416" t="n">
         <x:f>N13*'参数与来源'!$D$8</x:f>
@@ -5649,7 +5651,7 @@
       </x:c>
       <x:c r="O14" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N14))),"",N14*'参数与来源'!$N$19)</x:f>
-        <x:v>0.000030338987642076026</x:v>
+        <x:v>0.00003076607508643242</x:v>
       </x:c>
       <x:c r="P14" s="416" t="n">
         <x:f>N14*'参数与来源'!$D$8</x:f>
@@ -5710,7 +5712,7 @@
       </x:c>
       <x:c r="O15" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N15))),"",N15*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00005652836035963156</x:v>
+        <x:v>0.00005732412036469416</x:v>
       </x:c>
       <x:c r="P15" s="416" t="n">
         <x:f>N15*'参数与来源'!$D$8</x:f>
@@ -5771,7 +5773,7 @@
       </x:c>
       <x:c r="O16" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N16))),"",N16*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00006283971399338376</x:v>
+        <x:v>0.00006372432007088848</x:v>
       </x:c>
       <x:c r="P16" s="416" t="n">
         <x:f>N16*'参数与来源'!$D$8</x:f>
@@ -5832,7 +5834,7 @@
       </x:c>
       <x:c r="O17" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N17))),"",N17*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00007027022582111234</x:v>
+        <x:v>0.00007125943256440737</x:v>
       </x:c>
       <x:c r="P17" s="416" t="n">
         <x:f>N17*'参数与来源'!$D$8</x:f>
@@ -5893,7 +5895,7 @@
       </x:c>
       <x:c r="O18" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N18))),"",N18*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00007910103201070783</x:v>
+        <x:v>0.0000802145516180844</x:v>
       </x:c>
       <x:c r="P18" s="416" t="n">
         <x:f>N18*'参数与来源'!$D$8</x:f>
@@ -5954,7 +5956,7 @@
       </x:c>
       <x:c r="O19" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N19))),"",N19*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00008970742776859497</x:v>
+        <x:v>0.00009097025553719002</x:v>
       </x:c>
       <x:c r="P19" s="416" t="n">
         <x:f>N19*'参数与来源'!$D$8</x:f>
@@ -6015,7 +6017,7 @@
       </x:c>
       <x:c r="O20" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N20))),"",N20*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0001025994095756172</x:v>
+        <x:v>0.00010404372011574064</x:v>
       </x:c>
       <x:c r="P20" s="416" t="n">
         <x:f>N20*'参数与来源'!$D$8</x:f>
@@ -6076,7 +6078,7 @@
       </x:c>
       <x:c r="O21" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N21))),"",N21*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00011848414774782794</x:v>
+        <x:v>0.0001201520706348852</x:v>
       </x:c>
       <x:c r="P21" s="416" t="n">
         <x:f>N21*'参数与来源'!$D$8</x:f>
@@ -6137,7 +6139,7 @@
       </x:c>
       <x:c r="O22" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N22))),"",N22*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00013836507264308002</x:v>
+        <x:v>0.00014031286292403734</x:v>
       </x:c>
       <x:c r="P22" s="416" t="n">
         <x:f>N22*'参数与来源'!$D$8</x:f>
@@ -6198,7 +6200,7 @@
       </x:c>
       <x:c r="O23" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N23))),"",N23*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00016370432109572163</x:v>
+        <x:v>0.00016600881658356405</x:v>
       </x:c>
       <x:c r="P23" s="416" t="n">
         <x:f>N23*'参数与来源'!$D$8</x:f>
@@ -6259,7 +6261,7 @@
       </x:c>
       <x:c r="O24" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N24))),"",N24*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0001966994597781064</x:v>
+        <x:v>0.00019946843383136082</x:v>
       </x:c>
       <x:c r="P24" s="416" t="n">
         <x:f>N24*'参数与来源'!$D$8</x:f>
@@ -6320,7 +6322,7 @@
       </x:c>
       <x:c r="O25" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N25))),"",N25*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00024077652296966947</x:v>
+        <x:v>0.0002441659778542326</x:v>
       </x:c>
       <x:c r="P25" s="416" t="n">
         <x:f>N25*'参数与来源'!$D$8</x:f>
@@ -6381,7 +6383,7 @@
       </x:c>
       <x:c r="O26" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N26))),"",N26*'参数与来源'!$N$19)</x:f>
-        <x:v>0.00030151663222222216</x:v>
+        <x:v>0.0003057611366666666</x:v>
       </x:c>
       <x:c r="P26" s="416" t="n">
         <x:f>N26*'参数与来源'!$D$8</x:f>
@@ -6442,7 +6444,7 @@
       </x:c>
       <x:c r="O27" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N27))),"",N27*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0003885137613148283</x:v>
+        <x:v>0.0003939829401607012</x:v>
       </x:c>
       <x:c r="P27" s="416" t="n">
         <x:f>N27*'参数与来源'!$D$8</x:f>
@@ -6503,7 +6505,7 @@
       </x:c>
       <x:c r="O28" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N28))),"",N28*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0005194095109765626</x:v>
+        <x:v>0.0005267213330859376</x:v>
       </x:c>
       <x:c r="P28" s="416" t="n">
         <x:f>N28*'参数与来源'!$D$8</x:f>
@@ -6564,7 +6566,7 @@
       </x:c>
       <x:c r="O29" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N29))),"",N29*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0007295958014266093</x:v>
+        <x:v>0.0007398664541563761</x:v>
       </x:c>
       <x:c r="P29" s="416" t="n">
         <x:f>N29*'参数与来源'!$D$8</x:f>
@@ -6625,7 +6627,7 @@
       </x:c>
       <x:c r="O30" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N30))),"",N30*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0010989159901652857</x:v>
+        <x:v>0.001114385630330575</x:v>
       </x:c>
       <x:c r="P30" s="416" t="n">
         <x:f>N30*'参数与来源'!$D$8</x:f>
@@ -6686,7 +6688,7 @@
       </x:c>
       <x:c r="O31" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N31))),"",N31*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0018403990977162543</x:v>
+        <x:v>0.0018663067303806141</x:v>
       </x:c>
       <x:c r="P31" s="416" t="n">
         <x:f>N31*'参数与来源'!$D$8</x:f>
@@ -6747,7 +6749,7 @@
       </x:c>
       <x:c r="O32" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N32))),"",N32*'参数与来源'!$N$19)</x:f>
-        <x:v>0.0036935787447222035</x:v>
+        <x:v>0.003745573924166648</x:v>
       </x:c>
       <x:c r="P32" s="416" t="n">
         <x:f>N32*'参数与来源'!$D$8</x:f>
@@ -6808,7 +6810,7 @@
       </x:c>
       <x:c r="O33" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N33))),"",N33*'参数与来源'!$N$19)</x:f>
-        <x:v>0.010854598759999893</x:v>
+        <x:v>0.011007400919999891</x:v>
       </x:c>
       <x:c r="P33" s="416" t="n">
         <x:f>N33*'参数与来源'!$D$8</x:f>
@@ -6869,7 +6871,7 @@
       </x:c>
       <x:c r="O34" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N34))),"",N34*'参数与来源'!$N$19)</x:f>
-        <x:v>0.02127501356959979</x:v>
+        <x:v>0.021574505803199785</x:v>
       </x:c>
       <x:c r="P34" s="416" t="n">
         <x:f>N34*'参数与来源'!$D$8</x:f>
@@ -6930,7 +6932,7 @@
       </x:c>
       <x:c r="O35" s="411" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N35))),"",N35*'参数与来源'!$N$19)</x:f>
-        <x:v>0.1329688348099968</x:v>
+        <x:v>0.13484066126999675</x:v>
       </x:c>
       <x:c r="P35" s="416" t="n">
         <x:f>N35*'参数与来源'!$D$8</x:f>
@@ -6991,7 +6993,7 @@
       </x:c>
       <x:c r="O36" s="424" t="n">
         <x:f>IF(OR('参数与来源'!$N$19="",NOT(ISNUMBER(N36))),"",N36*'参数与来源'!$N$19)</x:f>
-        <x:v>2.127501356959795</x:v>
+        <x:v>2.157450580319792</x:v>
       </x:c>
       <x:c r="P36" s="429" t="n">
         <x:f>N36*'参数与来源'!$D$8</x:f>
@@ -7355,8 +7357,8 @@
       <x:c r="M8" t="str">
         <x:v>USDT / USD</x:v>
       </x:c>
-      <x:c r="N8" s="431">
-        <x:v>0.999164</x:v>
+      <x:c r="N8" s="431" t="n">
+        <x:v>0.99917</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="40" customHeight="1">
@@ -7388,10 +7390,8 @@
       <x:c r="M9" t="str">
         <x:v>汇率快照 / UTC</x:v>
       </x:c>
-      <x:c r="N9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-09-18T09:01:38.255Z</x:t>
-        </x:is>
+      <x:c r="N9" t="n">
+        <x:v>46283.40053702546</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="40" customHeight="1">
@@ -7423,10 +7423,8 @@
       <x:c r="M10" t="str">
         <x:v>汇率来源</x:v>
       </x:c>
-      <x:c r="N10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:t>
-        </x:is>
+      <x:c r="N10" t="str">
+        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="40" customHeight="1">
@@ -7491,8 +7489,8 @@
       <x:c r="M12" t="str">
         <x:v>BNB / USDT</x:v>
       </x:c>
-      <x:c r="N12">
-        <x:v>754.5107710045597</x:v>
+      <x:c r="N12" t="n">
+        <x:v>751.723930862616</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="40" customHeight="1">
@@ -7524,10 +7522,8 @@
       <x:c r="M13" t="str">
         <x:v>原生币价格时间 / UTC</x:v>
       </x:c>
-      <x:c r="N13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-09-18T09:01:38.255Z</x:t>
-        </x:is>
+      <x:c r="N13" t="n">
+        <x:v>46283.40053702546</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="40" customHeight="1">
@@ -7559,10 +7555,8 @@
       <x:c r="M14" t="str">
         <x:v>原生币价格来源</x:v>
       </x:c>
-      <x:c r="N14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
-        </x:is>
+      <x:c r="N14" t="str">
+        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="40" customHeight="1">
@@ -7595,7 +7589,7 @@
         <x:v>BNC4 / USDT 每日价格</x:v>
       </x:c>
       <x:c r="N15" s="434" t="n">
-        <x:v>5.7682</x:v>
+        <x:v>5.8494</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -7616,7 +7610,7 @@
         <x:v>BNC4 价格时间 / UTC</x:v>
       </x:c>
       <x:c r="N16" t="n">
-        <x:v>46283.396544745374</x:v>
+        <x:v>46283.40053702546</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -7680,7 +7674,7 @@
       </x:c>
       <x:c r="N19" s="434" t="n">
         <x:f>IF(AND(ISNUMBER('控筹模型'!$L$14),'控筹模型'!$L$14&gt;0),'控筹模型'!$L$14,IF(AND(ISNUMBER($N$15),$N$15&gt;0),$N$15,""))</x:f>
-        <x:v>5.7682</x:v>
+        <x:v>5.8494</x:v>
       </x:c>
     </x:row>
     <x:row r="20">

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R7b2608e940484796"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rce8ed05961904f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R07817fff46094703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R16d2ba0d60314fea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -772,7 +772,7 @@
         <v>买入税率</v>
       </c>
       <c r="J7" s="37" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,25,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,25,FALSE)</f>
         <v>0.03</v>
       </c>
       <c r="K7" s="32"/>
@@ -797,7 +797,7 @@
         <v>卖出税率</v>
       </c>
       <c r="J8" s="37" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,26,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,26,FALSE)</f>
         <v>0.03</v>
       </c>
       <c r="K8" s="32"/>
@@ -849,7 +849,7 @@
         <v>单地址 Gas</v>
       </c>
       <c r="G11" s="36" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,33,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,33,FALSE)</f>
         <v>0.01</v>
       </c>
       <c r="H11" s="32"/>
@@ -867,14 +867,14 @@
       </c>
       <c r="G12" s="45" t="n">
         <f>IF(AND(ISNUMBER($D$55),$D$55&gt;0),ROUNDUP($G$56/$D$55,0),"")</f>
-        <v>1710</v>
+        <v>1554</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="32" t="str">
         <v>洗筹基础费率</v>
       </c>
       <c r="J12" s="37" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,20,FALSE)</f>
         <v>0.0025</v>
       </c>
       <c r="K12" s="32"/>
@@ -950,10 +950,10 @@
       </c>
       <c r="D18" s="43" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>13378.553438509629</v>
+        <v>13186.95699378578</v>
       </c>
       <c r="E18" s="31" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F18" s="3" t="str">
@@ -964,7 +964,7 @@
         <v>2.2</v>
       </c>
       <c r="H18" s="31" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,4,FALSE)</f>
         <v>BNB</v>
       </c>
       <c r="I18" s="3" t="str">
@@ -972,7 +972,7 @@
       </c>
       <c r="J18" s="43" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>79910.30313111599</v>
+        <v>86549.82887660645</v>
       </c>
       <c r="K18" s="31" t="str">
         <v>USDT</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="D19" s="44" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>78256.51048321823</v>
+        <v>84893.67303889472</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="G19" s="44" t="n">
         <f>IF(G18=0,0,IF(AND(ISNUMBER(J44),J44&gt;0),G18*J44,""))</f>
-        <v>1653.7926478977554</v>
+        <v>1656.155837711734</v>
       </c>
       <c r="H19" s="3" t="str">
         <v>USDT</v>
@@ -1043,7 +1043,7 @@
         <v>4653.099415204678</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F22" s="3"/>
@@ -1065,7 +1065,7 @@
         <v>2080</v>
       </c>
       <c r="E23" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F23" s="3"/>
@@ -1090,7 +1090,7 @@
         <v>3397.694444444444</v>
       </c>
       <c r="E24" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F24" s="3"/>
@@ -1112,10 +1112,10 @@
       </c>
       <c r="D25" s="44" t="n">
         <f>IF($D$51="可达",$G$12,"")</f>
-        <v>1710</v>
+        <v>1554</v>
       </c>
       <c r="E25" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F25" s="3"/>
@@ -1136,11 +1136,11 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",IF($G$40="pons",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1+$G$42)),"")))</f>
-        <v>1537.759578860506</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
+        <v>1502.1631341366572</v>
       </c>
       <c r="E26" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="F26" s="3"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" s="40" t="n">
         <f>D8*J54</f>
-        <v>0.8425812425625</v>
+        <v>0.8446929750000001</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>目标持仓全部洗一轮，以卖出所得买回。补回为小单固定价 + 现有外盘曲线差额的保守预留，损耗仍按目标加缓冲 FDV；非逐笔模拟。Pons 按原批准口径持仓不降、补回为 0。</v>
+        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1313,11 +1313,11 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="44" t="n">
-        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,23,FALSE))</f>
+        <f>IF($G$40="four-stock",E126,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,23,FALSE))</f>
         <v>402.43927478800083</v>
       </c>
       <c r="H37" s="3" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
       </c>
       <c r="I37" s="3"/>
@@ -1359,7 +1359,7 @@
         <v>模型类型</v>
       </c>
       <c r="G40" s="32" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,10,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,10,FALSE)</f>
         <v>four-stock</v>
       </c>
       <c r="H40" s="32"/>
@@ -1376,7 +1376,7 @@
         <v>内盘基础费</v>
       </c>
       <c r="G41" s="39" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,19,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,19,FALSE)</f>
         <v>0.01</v>
       </c>
       <c r="H41" s="32"/>
@@ -1398,7 +1398,7 @@
         <v>外盘基础费</v>
       </c>
       <c r="G42" s="39" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,20,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,20,FALSE)</f>
         <v>0.0025</v>
       </c>
       <c r="H42" s="32"/>
@@ -1415,7 +1415,7 @@
         <v>毕业控筹率</v>
       </c>
       <c r="G43" s="39" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,15,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,15,FALSE)</f>
         <v>0.8</v>
       </c>
       <c r="H43" s="32"/>
@@ -1423,7 +1423,7 @@
         <v>模型键</v>
       </c>
       <c r="J43" s="32" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,2,FALSE)</f>
         <v>fourmeme-bnc4</v>
       </c>
       <c r="K43" s="32"/>
@@ -1437,7 +1437,7 @@
         <v>内盘初始 TOKEN</v>
       </c>
       <c r="G44" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,12,FALSE)</f>
         <v>1073972601.740811</v>
       </c>
       <c r="H44" s="32"/>
@@ -1445,8 +1445,8 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J44" s="32" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,7,FALSE))</f>
-        <v>751.723930862616</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)=VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,4,FALSE),$D$55,VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,7,FALSE))</f>
+        <v>752.7981080507881</v>
       </c>
       <c r="K44" s="32"/>
       <c r="L44" s="32"/>
@@ -1456,7 +1456,7 @@
         <v>总供应量</v>
       </c>
       <c r="D45" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,11,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,11,FALSE)</f>
         <v>1000000000</v>
       </c>
       <c r="E45" s="32"/>
@@ -1464,7 +1464,7 @@
         <v>内盘初始 Quote</v>
       </c>
       <c r="G45" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,13,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,13,FALSE)</f>
         <v>684.9315068493152</v>
       </c>
       <c r="H45" s="32"/>
@@ -1472,7 +1472,7 @@
         <v>税率上限</v>
       </c>
       <c r="J45" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,32,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,32,FALSE)</f>
         <v>0.1</v>
       </c>
       <c r="K45" s="32"/>
@@ -1486,7 +1486,7 @@
         <v>内盘 K</v>
       </c>
       <c r="G46" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,14,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,14,FALSE)</f>
         <v>735597672425.2131</v>
       </c>
       <c r="H46" s="32"/>
@@ -1525,7 +1525,7 @@
         <v>外盘初始 TOKEN</v>
       </c>
       <c r="G48" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,16,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,16,FALSE)</f>
         <v>200000000</v>
       </c>
       <c r="H48" s="32"/>
@@ -1547,7 +1547,7 @@
         <v>外盘初始 Quote</v>
       </c>
       <c r="G49" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,17,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,17,FALSE)</f>
         <v>1960</v>
       </c>
       <c r="H49" s="32"/>
@@ -1564,7 +1564,7 @@
         <v>外盘 K</v>
       </c>
       <c r="G50" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,18,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,18,FALSE)</f>
         <v>392000000000</v>
       </c>
       <c r="H50" s="32"/>
@@ -1591,7 +1591,7 @@
         <v>永久锁仓 TOKEN</v>
       </c>
       <c r="G51" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,22,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,22,FALSE)</f>
         <v>0</v>
       </c>
       <c r="H51" s="32"/>
@@ -1618,7 +1618,7 @@
         <v>一套内盘原值</v>
       </c>
       <c r="G52" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,21,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,21,FALSE)</f>
         <v>2080</v>
       </c>
       <c r="H52" s="32"/>
@@ -1645,7 +1645,7 @@
         <v>内盘募集 Quote</v>
       </c>
       <c r="G53" s="32" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,24,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,24,FALSE)</f>
         <v>2000</v>
       </c>
       <c r="H53" s="32"/>
@@ -1675,8 +1675,8 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="39" t="n">
-        <f>IF($G$40="pons",1,(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))^2)</f>
-        <v>0.936201380625</v>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
+        <v>0.93854775</v>
       </c>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
@@ -1686,15 +1686,15 @@
         <v>有效价格 / USDT</v>
       </c>
       <c r="D55" s="41" t="n">
-        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,6,FALSE),""))</f>
-        <v>5.8494</v>
+        <f>IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,IF(AND(ISNUMBER(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE)),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE)&gt;0),VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,6,FALSE),""))</f>
+        <v>6.4377</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="32" t="str">
         <v>价格来源</v>
       </c>
       <c r="G55" s="32" t="str">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,9,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,9,FALSE)</f>
         <v>https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</v>
       </c>
       <c r="H55" s="32"/>
@@ -1702,7 +1702,7 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="32" t="n">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
         <v>96907216.49484538</v>
       </c>
       <c r="K55" s="32"/>
@@ -1713,8 +1713,8 @@
         <v>价格时间 / UTC</v>
       </c>
       <c r="D56" s="42" t="n">
-        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AI$14,8,FALSE)</f>
-        <v>46283.40053702546</v>
+        <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,8,FALSE)</f>
+        <v>46285.27349457176</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="32" t="str">
@@ -1729,8 +1729,8 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="32" t="n">
-        <f>IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
-        <v>156101811.79123718</v>
+        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
+        <v>153924768.0412371</v>
       </c>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="G59" s="59" t="n">
         <f>IF(AND(ISNUMBER(F59),ISNUMBER($D$55)),F59*$D$55,"")</f>
-        <v>0.0000037304846973473208</v>
+        <v>0.000004105676024226903</v>
       </c>
       <c r="H59" s="56" t="n">
         <f>IF(ISNUMBER(F59),F59*$D$45,"")</f>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="I59" s="56" t="n">
         <f>IF(AND(ISNUMBER(H59),ISNUMBER($D$55)),H59*$D$55,"")</f>
-        <v>3730.484697347321</v>
+        <v>4105.676024226903</v>
       </c>
       <c r="J59" s="56" t="n">
         <f>0</f>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="G60" s="60" t="n">
         <f>IF(AND(ISNUMBER(F60),ISNUMBER($D$55)),F60*$D$55,"")</f>
-        <v>0.000004535844806784795</v>
+        <v>0.0000049920347578620835</v>
       </c>
       <c r="H60" s="57" t="n">
         <f>IF(ISNUMBER(F60),F60*$D$45,"")</f>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="I60" s="57" t="n">
         <f>IF(AND(ISNUMBER(H60),ISNUMBER($D$55)),H60*$D$55,"")</f>
-        <v>4535.844806784795</v>
+        <v>4992.034757862084</v>
       </c>
       <c r="J60" s="57" t="n">
         <f>E60-E59</f>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G61" s="60" t="n">
         <f>IF(AND(ISNUMBER(F61),ISNUMBER($D$55)),F61*$D$55,"")</f>
-        <v>0.000005633211159257515</v>
+        <v>0.000006199768092445739</v>
       </c>
       <c r="H61" s="57" t="n">
         <f>IF(ISNUMBER(F61),F61*$D$45,"")</f>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I61" s="57" t="n">
         <f>IF(AND(ISNUMBER(H61),ISNUMBER($D$55)),H61*$D$55,"")</f>
-        <v>5633.211159257515</v>
+        <v>6199.768092445738</v>
       </c>
       <c r="J61" s="57" t="n">
         <f>E61-E60</f>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G62" s="60" t="n">
         <f>IF(AND(ISNUMBER(F62),ISNUMBER($D$55)),F62*$D$55,"")</f>
-        <v>0.000007182911124711535</v>
+        <v>0.000007905328229827923</v>
       </c>
       <c r="H62" s="57" t="n">
         <f>IF(ISNUMBER(F62),F62*$D$45,"")</f>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="I62" s="57" t="n">
         <f>IF(AND(ISNUMBER(H62),ISNUMBER($D$55)),H62*$D$55,"")</f>
-        <v>7182.911124711535</v>
+        <v>7905.328229827924</v>
       </c>
       <c r="J62" s="57" t="n">
         <f>E62-E61</f>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G63" s="60" t="n">
         <f>IF(AND(ISNUMBER(F63),ISNUMBER($D$55)),F63*$D$55,"")</f>
-        <v>0.000009472556037511687</v>
+        <v>0.000010425252846905493</v>
       </c>
       <c r="H63" s="57" t="n">
         <f>IF(ISNUMBER(F63),F63*$D$45,"")</f>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="I63" s="57" t="n">
         <f>IF(AND(ISNUMBER(H63),ISNUMBER($D$55)),H63*$D$55,"")</f>
-        <v>9472.556037511687</v>
+        <v>10425.252846905492</v>
       </c>
       <c r="J63" s="57" t="n">
         <f>E63-E62</f>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G64" s="60" t="n">
         <f>IF(AND(ISNUMBER(F64),ISNUMBER($D$55)),F64*$D$55,"")</f>
-        <v>0.000013060786882328206</v>
+        <v>0.000014374367920190838</v>
       </c>
       <c r="H64" s="57" t="n">
         <f>IF(ISNUMBER(F64),F64*$D$45,"")</f>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I64" s="57" t="n">
         <f>IF(AND(ISNUMBER(H64),ISNUMBER($D$55)),H64*$D$55,"")</f>
-        <v>13060.786882328206</v>
+        <v>14374.36792019084</v>
       </c>
       <c r="J64" s="57" t="n">
         <f>E64-E63</f>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G65" s="60" t="n">
         <f>IF(AND(ISNUMBER(F65),ISNUMBER($D$55)),F65*$D$55,"")</f>
-        <v>0.000019153369704402947</v>
+        <v>0.000021079708713036356</v>
       </c>
       <c r="H65" s="57" t="n">
         <f>IF(ISNUMBER(F65),F65*$D$45,"")</f>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="I65" s="57" t="n">
         <f>IF(AND(ISNUMBER(H65),ISNUMBER($D$55)),H65*$D$55,"")</f>
-        <v>19153.36970440295</v>
+        <v>21079.708713036358</v>
       </c>
       <c r="J65" s="57" t="n">
         <f>E65-E64</f>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G66" s="60" t="n">
         <f>IF(AND(ISNUMBER(F66),ISNUMBER($D$55)),F66*$D$55,"")</f>
-        <v>0.00003076607508643242</v>
+        <v>0.00003386035517898007</v>
       </c>
       <c r="H66" s="57" t="n">
         <f>IF(ISNUMBER(F66),F66*$D$45,"")</f>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="I66" s="57" t="n">
         <f>IF(AND(ISNUMBER(H66),ISNUMBER($D$55)),H66*$D$55,"")</f>
-        <v>30766.07508643242</v>
+        <v>33860.35517898007</v>
       </c>
       <c r="J66" s="57" t="n">
         <f>E66-E65</f>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G67" s="61" t="n">
         <f>IF(AND(ISNUMBER(F67),ISNUMBER($D$55)),F67*$D$55,"")</f>
-        <v>0.00005732412036469416</v>
+        <v>0.00006308946040137306</v>
       </c>
       <c r="H67" s="58" t="n">
         <f>IF(ISNUMBER(F67),F67*$D$45,"")</f>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="I67" s="58" t="n">
         <f>IF(AND(ISNUMBER(H67),ISNUMBER($D$55)),H67*$D$55,"")</f>
-        <v>57324.12036469415</v>
+        <v>63089.46040137306</v>
       </c>
       <c r="J67" s="58" t="n">
         <f>E67-E66</f>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="G72" s="59" t="n">
         <f>IF(AND(ISNUMBER(F72),ISNUMBER($D$55)),F72*$D$55,"")</f>
-        <v>0.00005732412</v>
+        <v>0.00006308946</v>
       </c>
       <c r="H72" s="56" t="n">
         <f>IF(ISNUMBER(F72),F72*$D$45,"")</f>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="I72" s="56" t="n">
         <f>IF(AND(ISNUMBER(H72),ISNUMBER($D$55)),H72*$D$55,"")</f>
-        <v>57324.12</v>
+        <v>63089.46000000001</v>
       </c>
       <c r="J72" s="56" t="n">
         <f>IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),0,E72-$G$49)</f>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="G73" s="60" t="n">
         <f>IF(AND(ISNUMBER(F73),ISNUMBER($D$55)),F73*$D$55,"")</f>
-        <v>0.00006039726156378602</v>
+        <v>0.00006647168098765434</v>
       </c>
       <c r="H73" s="57" t="n">
         <f>IF(ISNUMBER(F73),F73*$D$45,"")</f>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="I73" s="57" t="n">
         <f>IF(AND(ISNUMBER(H73),ISNUMBER($D$55)),H73*$D$55,"")</f>
-        <v>60397.261563786014</v>
+        <v>66471.68098765433</v>
       </c>
       <c r="J73" s="57" t="n">
         <f>IF(D73="","",E73-E72)</f>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G74" s="60" t="n">
         <f>IF(AND(ISNUMBER(F74),ISNUMBER($D$55)),F74*$D$55,"")</f>
-        <v>0.00006372432007088848</v>
+        <v>0.00007013335646739133</v>
       </c>
       <c r="H74" s="57" t="n">
         <f>IF(ISNUMBER(F74),F74*$D$45,"")</f>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I74" s="57" t="n">
         <f>IF(AND(ISNUMBER(H74),ISNUMBER($D$55)),H74*$D$55,"")</f>
-        <v>63724.32007088849</v>
+        <v>70133.35646739134</v>
       </c>
       <c r="J74" s="57" t="n">
         <f>IF(D74="","",E74-E73)</f>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G75" s="60" t="n">
         <f>IF(AND(ISNUMBER(F75),ISNUMBER($D$55)),F75*$D$55,"")</f>
-        <v>0.00006733405887207017</v>
+        <v>0.00007410614264723324</v>
       </c>
       <c r="H75" s="57" t="n">
         <f>IF(ISNUMBER(F75),F75*$D$45,"")</f>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="I75" s="57" t="n">
         <f>IF(AND(ISNUMBER(H75),ISNUMBER($D$55)),H75*$D$55,"")</f>
-        <v>67334.05887207018</v>
+        <v>74106.14264723325</v>
       </c>
       <c r="J75" s="57" t="n">
         <f>IF(D75="","",E75-E74)</f>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G76" s="60" t="n">
         <f>IF(AND(ISNUMBER(F76),ISNUMBER($D$55)),F76*$D$55,"")</f>
-        <v>0.00007125943256440746</v>
+        <v>0.00007842630851367421</v>
       </c>
       <c r="H76" s="57" t="n">
         <f>IF(ISNUMBER(F76),F76*$D$45,"")</f>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="I76" s="57" t="n">
         <f>IF(AND(ISNUMBER(H76),ISNUMBER($D$55)),H76*$D$55,"")</f>
-        <v>71259.43256440746</v>
+        <v>78426.3085136742</v>
       </c>
       <c r="J76" s="57" t="n">
         <f>IF(D76="","",E76-E75)</f>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G77" s="60" t="n">
         <f>IF(AND(ISNUMBER(F77),ISNUMBER($D$55)),F77*$D$55,"")</f>
-        <v>0.0000755383418059592</v>
+        <v>0.00008313556656139494</v>
       </c>
       <c r="H77" s="57" t="n">
         <f>IF(ISNUMBER(F77),F77*$D$45,"")</f>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I77" s="57" t="n">
         <f>IF(AND(ISNUMBER(H77),ISNUMBER($D$55)),H77*$D$55,"")</f>
-        <v>75538.3418059592</v>
+        <v>83135.56656139494</v>
       </c>
       <c r="J77" s="57" t="n">
         <f>IF(D77="","",E77-E76)</f>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G78" s="60" t="n">
         <f>IF(AND(ISNUMBER(F78),ISNUMBER($D$55)),F78*$D$55,"")</f>
-        <v>0.0000802145516180845</v>
+        <v>0.00008828208345330165</v>
       </c>
       <c r="H78" s="57" t="n">
         <f>IF(ISNUMBER(F78),F78*$D$45,"")</f>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="I78" s="57" t="n">
         <f>IF(AND(ISNUMBER(H78),ISNUMBER($D$55)),H78*$D$55,"")</f>
-        <v>80214.55161808452</v>
+        <v>88282.08345330165</v>
       </c>
       <c r="J78" s="57" t="n">
         <f>IF(D78="","",E78-E77)</f>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G79" s="60" t="n">
         <f>IF(AND(ISNUMBER(F79),ISNUMBER($D$55)),F79*$D$55,"")</f>
-        <v>0.00008533881493295363</v>
+        <v>0.00009392171656817376</v>
       </c>
       <c r="H79" s="57" t="n">
         <f>IF(ISNUMBER(F79),F79*$D$45,"")</f>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="I79" s="57" t="n">
         <f>IF(AND(ISNUMBER(H79),ISNUMBER($D$55)),H79*$D$55,"")</f>
-        <v>85338.81493295362</v>
+        <v>93921.71656817377</v>
       </c>
       <c r="J79" s="57" t="n">
         <f>IF(D79="","",E79-E78)</f>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="G80" s="60" t="n">
         <f>IF(AND(ISNUMBER(F80),ISNUMBER($D$55)),F80*$D$55,"")</f>
-        <v>0.00009097025553719011</v>
+        <v>0.00010011953603305789</v>
       </c>
       <c r="H80" s="57" t="n">
         <f>IF(ISNUMBER(F80),F80*$D$45,"")</f>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I80" s="57" t="n">
         <f>IF(AND(ISNUMBER(H80),ISNUMBER($D$55)),H80*$D$55,"")</f>
-        <v>90970.25553719011</v>
+        <v>100119.53603305788</v>
       </c>
       <c r="J80" s="57" t="n">
         <f>IF(D80="","",E80-E79)</f>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="G81" s="60" t="n">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER($D$55)),F81*$D$55,"")</f>
-        <v>0.0000971780811819288</v>
+        <v>0.00010695171012837265</v>
       </c>
       <c r="H81" s="57" t="n">
         <f>IF(ISNUMBER(F81),F81*$D$45,"")</f>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="I81" s="57" t="n">
         <f>IF(AND(ISNUMBER(H81),ISNUMBER($D$55)),H81*$D$55,"")</f>
-        <v>97178.08118192879</v>
+        <v>106951.71012837265</v>
       </c>
       <c r="J81" s="57" t="n">
         <f>IF(D81="","",E81-E80)</f>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="G82" s="60" t="n">
         <f>IF(AND(ISNUMBER(F82),ISNUMBER($D$55)),F82*$D$55,"")</f>
-        <v>0.00010404372011574082</v>
+        <v>0.00011450785670138898</v>
       </c>
       <c r="H82" s="57" t="n">
         <f>IF(ISNUMBER(F82),F82*$D$45,"")</f>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="I82" s="57" t="n">
         <f>IF(AND(ISNUMBER(H82),ISNUMBER($D$55)),H82*$D$55,"")</f>
-        <v>104043.72011574083</v>
+        <v>114507.85670138898</v>
       </c>
       <c r="J82" s="57" t="n">
         <f>IF(D82="","",E82-E81)</f>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="G83" s="60" t="n">
         <f>IF(AND(ISNUMBER(F83),ISNUMBER($D$55)),F83*$D$55,"")</f>
-        <v>0.00011166350501112786</v>
+        <v>0.0001228939970270691</v>
       </c>
       <c r="H83" s="57" t="n">
         <f>IF(ISNUMBER(F83),F83*$D$45,"")</f>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="I83" s="57" t="n">
         <f>IF(AND(ISNUMBER(H83),ISNUMBER($D$55)),H83*$D$55,"")</f>
-        <v>111663.50501112788</v>
+        <v>122893.9970270691</v>
       </c>
       <c r="J83" s="57" t="n">
         <f>IF(D83="","",E83-E82)</f>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G84" s="60" t="n">
         <f>IF(AND(ISNUMBER(F84),ISNUMBER($D$55)),F84*$D$55,"")</f>
-        <v>0.00012015207063488539</v>
+        <v>0.00013223629519714872</v>
       </c>
       <c r="H84" s="57" t="n">
         <f>IF(ISNUMBER(F84),F84*$D$45,"")</f>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="I84" s="57" t="n">
         <f>IF(AND(ISNUMBER(H84),ISNUMBER($D$55)),H84*$D$55,"")</f>
-        <v>120152.07063488539</v>
+        <v>132236.29519714872</v>
       </c>
       <c r="J84" s="57" t="n">
         <f>IF(D84="","",E84-E83)</f>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G85" s="60" t="n">
         <f>IF(AND(ISNUMBER(F85),ISNUMBER($D$55)),F85*$D$55,"")</f>
-        <v>0.00012964669072291322</v>
+        <v>0.0001426858311736073</v>
       </c>
       <c r="H85" s="57" t="n">
         <f>IF(ISNUMBER(F85),F85*$D$45,"")</f>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I85" s="57" t="n">
         <f>IF(AND(ISNUMBER(H85),ISNUMBER($D$55)),H85*$D$55,"")</f>
-        <v>129646.6907229132</v>
+        <v>142685.83117360726</v>
       </c>
       <c r="J85" s="57" t="n">
         <f>IF(D85="","",E85-E84)</f>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="G86" s="60" t="n">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER($D$55)),F86*$D$55,"")</f>
-        <v>0.00014031286292403759</v>
+        <v>0.00015442474743496373</v>
       </c>
       <c r="H86" s="57" t="n">
         <f>IF(ISNUMBER(F86),F86*$D$45,"")</f>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I86" s="57" t="n">
         <f>IF(AND(ISNUMBER(H86),ISNUMBER($D$55)),H86*$D$55,"")</f>
-        <v>140312.8629240376</v>
+        <v>154424.74743496373</v>
       </c>
       <c r="J86" s="57" t="n">
         <f>IF(D86="","",E86-E85)</f>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G87" s="60" t="n">
         <f>IF(AND(ISNUMBER(F87),ISNUMBER($D$55)),F87*$D$55,"")</f>
-        <v>0.00015235156982698953</v>
+        <v>0.00016767424027681652</v>
       </c>
       <c r="H87" s="57" t="n">
         <f>IF(ISNUMBER(F87),F87*$D$45,"")</f>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="I87" s="57" t="n">
         <f>IF(AND(ISNUMBER(H87),ISNUMBER($D$55)),H87*$D$55,"")</f>
-        <v>152351.56982698952</v>
+        <v>167674.2402768165</v>
       </c>
       <c r="J87" s="57" t="n">
         <f>IF(D87="","",E87-E86)</f>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="G88" s="60" t="n">
         <f>IF(AND(ISNUMBER(F88),ISNUMBER($D$55)),F88*$D$55,"")</f>
-        <v>0.00016600881658356405</v>
+        <v>0.00018270505667590016</v>
       </c>
       <c r="H88" s="57" t="n">
         <f>IF(ISNUMBER(F88),F88*$D$45,"")</f>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="I88" s="57" t="n">
         <f>IF(AND(ISNUMBER(H88),ISNUMBER($D$55)),H88*$D$55,"")</f>
-        <v>166008.81658356404</v>
+        <v>182705.05667590015</v>
       </c>
       <c r="J88" s="57" t="n">
         <f>IF(D88="","",E88-E87)</f>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="G89" s="60" t="n">
         <f>IF(AND(ISNUMBER(F89),ISNUMBER($D$55)),F89*$D$55,"")</f>
-        <v>0.00018158829899166728</v>
+        <v>0.0001998514364582105</v>
       </c>
       <c r="H89" s="57" t="n">
         <f>IF(ISNUMBER(F89),F89*$D$45,"")</f>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="I89" s="57" t="n">
         <f>IF(AND(ISNUMBER(H89),ISNUMBER($D$55)),H89*$D$55,"")</f>
-        <v>181588.29899166728</v>
+        <v>199851.4364582105</v>
       </c>
       <c r="J89" s="57" t="n">
         <f>IF(D89="","",E89-E88)</f>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G90" s="60" t="n">
         <f>IF(AND(ISNUMBER(F90),ISNUMBER($D$55)),F90*$D$55,"")</f>
-        <v>0.00019946843383136082</v>
+        <v>0.00021952985545118332</v>
       </c>
       <c r="H90" s="57" t="n">
         <f>IF(ISNUMBER(F90),F90*$D$45,"")</f>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="I90" s="57" t="n">
         <f>IF(AND(ISNUMBER(H90),ISNUMBER($D$55)),H90*$D$55,"")</f>
-        <v>199468.43383136083</v>
+        <v>219529.8554511833</v>
       </c>
       <c r="J90" s="57" t="n">
         <f>IF(D90="","",E90-E89)</f>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="G91" s="60" t="n">
         <f>IF(AND(ISNUMBER(F91),ISNUMBER($D$55)),F91*$D$55,"")</f>
-        <v>0.00022012555660850925</v>
+        <v>0.00024226455632690534</v>
       </c>
       <c r="H91" s="57" t="n">
         <f>IF(ISNUMBER(F91),F91*$D$45,"")</f>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="I91" s="57" t="n">
         <f>IF(AND(ISNUMBER(H91),ISNUMBER($D$55)),H91*$D$55,"")</f>
-        <v>220125.55660850924</v>
+        <v>242264.55632690532</v>
       </c>
       <c r="J91" s="57" t="n">
         <f>IF(D91="","",E91-E90)</f>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G92" s="60" t="n">
         <f>IF(AND(ISNUMBER(F92),ISNUMBER($D$55)),F92*$D$55,"")</f>
-        <v>0.0002441659778542326</v>
+        <v>0.00026872282894522403</v>
       </c>
       <c r="H92" s="57" t="n">
         <f>IF(ISNUMBER(F92),F92*$D$45,"")</f>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="I92" s="57" t="n">
         <f>IF(AND(ISNUMBER(H92),ISNUMBER($D$55)),H92*$D$55,"")</f>
-        <v>244165.97785423262</v>
+        <v>268722.828945224</v>
       </c>
       <c r="J92" s="57" t="n">
         <f>IF(D92="","",E92-E91)</f>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="G93" s="60" t="n">
         <f>IF(AND(ISNUMBER(F93),ISNUMBER($D$55)),F93*$D$55,"")</f>
-        <v>0.0002723709860270167</v>
+        <v>0.0002997645393965407</v>
       </c>
       <c r="H93" s="57" t="n">
         <f>IF(ISNUMBER(F93),F93*$D$45,"")</f>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I93" s="57" t="n">
         <f>IF(AND(ISNUMBER(H93),ISNUMBER($D$55)),H93*$D$55,"")</f>
-        <v>272370.9860270167</v>
+        <v>299764.5393965408</v>
       </c>
       <c r="J93" s="57" t="n">
         <f>IF(D93="","",E93-E92)</f>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="G94" s="60" t="n">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER($D$55)),F94*$D$55,"")</f>
-        <v>0.0003057611366666666</v>
+        <v>0.00033651288499999995</v>
       </c>
       <c r="H94" s="57" t="n">
         <f>IF(ISNUMBER(F94),F94*$D$45,"")</f>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="I94" s="57" t="n">
         <f>IF(AND(ISNUMBER(H94),ISNUMBER($D$55)),H94*$D$55,"")</f>
-        <v>305761.1366666666</v>
+        <v>336512.88499999995</v>
       </c>
       <c r="J94" s="57" t="n">
         <f>IF(D94="","",E94-E93)</f>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G95" s="60" t="n">
         <f>IF(AND(ISNUMBER(F95),ISNUMBER($D$55)),F95*$D$55,"")</f>
-        <v>0.0003456898862874538</v>
+        <v>0.00038045744537093404</v>
       </c>
       <c r="H95" s="57" t="n">
         <f>IF(ISNUMBER(F95),F95*$D$45,"")</f>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="I95" s="57" t="n">
         <f>IF(AND(ISNUMBER(H95),ISNUMBER($D$55)),H95*$D$55,"")</f>
-        <v>345689.8862874538</v>
+        <v>380457.44537093403</v>
       </c>
       <c r="J95" s="57" t="n">
         <f>IF(D95="","",E95-E94)</f>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G96" s="60" t="n">
         <f>IF(AND(ISNUMBER(F96),ISNUMBER($D$55)),F96*$D$55,"")</f>
-        <v>0.0003939829401607012</v>
+        <v>0.0004336075450255661</v>
       </c>
       <c r="H96" s="57" t="n">
         <f>IF(ISNUMBER(F96),F96*$D$45,"")</f>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I96" s="57" t="n">
         <f>IF(AND(ISNUMBER(H96),ISNUMBER($D$55)),H96*$D$55,"")</f>
-        <v>393982.94016070117</v>
+        <v>433607.54502556607</v>
       </c>
       <c r="J96" s="57" t="n">
         <f>IF(D96="","",E96-E95)</f>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="G97" s="60" t="n">
         <f>IF(AND(ISNUMBER(F97),ISNUMBER($D$55)),F97*$D$55,"")</f>
-        <v>0.0004531507205040959</v>
+        <v>0.0004987260904347827</v>
       </c>
       <c r="H97" s="57" t="n">
         <f>IF(ISNUMBER(F97),F97*$D$45,"")</f>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="I97" s="57" t="n">
         <f>IF(AND(ISNUMBER(H97),ISNUMBER($D$55)),H97*$D$55,"")</f>
-        <v>453150.7205040959</v>
+        <v>498726.09043478273</v>
       </c>
       <c r="J97" s="57" t="n">
         <f>IF(D97="","",E97-E96)</f>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="G98" s="60" t="n">
         <f>IF(AND(ISNUMBER(F98),ISNUMBER($D$55)),F98*$D$55,"")</f>
-        <v>0.0005267213330859376</v>
+        <v>0.0005796960245507813</v>
       </c>
       <c r="H98" s="57" t="n">
         <f>IF(ISNUMBER(F98),F98*$D$45,"")</f>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="I98" s="57" t="n">
         <f>IF(AND(ISNUMBER(H98),ISNUMBER($D$55)),H98*$D$55,"")</f>
-        <v>526721.3330859375</v>
+        <v>579696.0245507812</v>
       </c>
       <c r="J98" s="57" t="n">
         <f>IF(D98="","",E98-E97)</f>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G99" s="60" t="n">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER($D$55)),F99*$D$55,"")</f>
-        <v>0.000619778965906349</v>
+        <v>0.0006821128746222353</v>
       </c>
       <c r="H99" s="57" t="n">
         <f>IF(ISNUMBER(F99),F99*$D$45,"")</f>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="I99" s="57" t="n">
         <f>IF(AND(ISNUMBER(H99),ISNUMBER($D$55)),H99*$D$55,"")</f>
-        <v>619778.965906349</v>
+        <v>682112.8746222352</v>
       </c>
       <c r="J99" s="57" t="n">
         <f>IF(D99="","",E99-E98)</f>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G100" s="60" t="n">
         <f>IF(AND(ISNUMBER(F100),ISNUMBER($D$55)),F100*$D$55,"")</f>
-        <v>0.0007398664541563785</v>
+        <v>0.0008142780920987653</v>
       </c>
       <c r="H100" s="57" t="n">
         <f>IF(ISNUMBER(F100),F100*$D$45,"")</f>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="I100" s="57" t="n">
         <f>IF(AND(ISNUMBER(H100),ISNUMBER($D$55)),H100*$D$55,"")</f>
-        <v>739866.4541563784</v>
+        <v>814278.0920987653</v>
       </c>
       <c r="J100" s="57" t="n">
         <f>IF(D100="","",E100-E99)</f>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="G101" s="60" t="n">
         <f>IF(AND(ISNUMBER(F101),ISNUMBER($D$55)),F101*$D$55,"")</f>
-        <v>0.0008985633404081644</v>
+        <v>0.0009889358253061238</v>
       </c>
       <c r="H101" s="57" t="n">
         <f>IF(ISNUMBER(F101),F101*$D$45,"")</f>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I101" s="57" t="n">
         <f>IF(AND(ISNUMBER(H101),ISNUMBER($D$55)),H101*$D$55,"")</f>
-        <v>898563.3404081645</v>
+        <v>988935.8253061238</v>
       </c>
       <c r="J101" s="57" t="n">
         <f>IF(D101="","",E101-E100)</f>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G102" s="60" t="n">
         <f>IF(AND(ISNUMBER(F102),ISNUMBER($D$55)),F102*$D$55,"")</f>
-        <v>0.001114385630330581</v>
+        <v>0.0012264643164049613</v>
       </c>
       <c r="H102" s="57" t="n">
         <f>IF(ISNUMBER(F102),F102*$D$45,"")</f>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="I102" s="57" t="n">
         <f>IF(AND(ISNUMBER(H102),ISNUMBER($D$55)),H102*$D$55,"")</f>
-        <v>1114385.630330581</v>
+        <v>1226464.3164049613</v>
       </c>
       <c r="J102" s="57" t="n">
         <f>IF(D102="","",E102-E101)</f>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G103" s="60" t="n">
         <f>IF(AND(ISNUMBER(F103),ISNUMBER($D$55)),F103*$D$55,"")</f>
-        <v>0.001418442196134124</v>
+        <v>0.0015611011943195286</v>
       </c>
       <c r="H103" s="57" t="n">
         <f>IF(ISNUMBER(F103),F103*$D$45,"")</f>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="I103" s="57" t="n">
         <f>IF(AND(ISNUMBER(H103),ISNUMBER($D$55)),H103*$D$55,"")</f>
-        <v>1418442.1961341242</v>
+        <v>1561101.1943195288</v>
       </c>
       <c r="J103" s="57" t="n">
         <f>IF(D103="","",E103-E102)</f>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G104" s="60" t="n">
         <f>IF(AND(ISNUMBER(F104),ISNUMBER($D$55)),F104*$D$55,"")</f>
-        <v>0.0018663067303806267</v>
+        <v>0.002054009443391008</v>
       </c>
       <c r="H104" s="57" t="n">
         <f>IF(ISNUMBER(F104),F104*$D$45,"")</f>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I104" s="57" t="n">
         <f>IF(AND(ISNUMBER(H104),ISNUMBER($D$55)),H104*$D$55,"")</f>
-        <v>1866306.7303806269</v>
+        <v>2054009.4433910078</v>
       </c>
       <c r="J104" s="57" t="n">
         <f>IF(D104="","",E104-E103)</f>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G105" s="60" t="n">
         <f>IF(AND(ISNUMBER(F105),ISNUMBER($D$55)),F105*$D$55,"")</f>
-        <v>0.002565339572318676</v>
+        <v>0.00282334710649228</v>
       </c>
       <c r="H105" s="57" t="n">
         <f>IF(ISNUMBER(F105),F105*$D$45,"")</f>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="I105" s="57" t="n">
         <f>IF(AND(ISNUMBER(H105),ISNUMBER($D$55)),H105*$D$55,"")</f>
-        <v>2565339.5723186764</v>
+        <v>2823347.10649228</v>
       </c>
       <c r="J105" s="57" t="n">
         <f>IF(D105="","",E105-E104)</f>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="G106" s="60" t="n">
         <f>IF(AND(ISNUMBER(F106),ISNUMBER($D$55)),F106*$D$55,"")</f>
-        <v>0.003745573924166675</v>
+        <v>0.0041222828412500094</v>
       </c>
       <c r="H106" s="57" t="n">
         <f>IF(ISNUMBER(F106),F106*$D$45,"")</f>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="I106" s="57" t="n">
         <f>IF(AND(ISNUMBER(H106),ISNUMBER($D$55)),H106*$D$55,"")</f>
-        <v>3745573.924166675</v>
+        <v>4122282.8412500094</v>
       </c>
       <c r="J106" s="57" t="n">
         <f>IF(D106="","",E106-E105)</f>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="G107" s="60" t="n">
         <f>IF(AND(ISNUMBER(F107),ISNUMBER($D$55)),F107*$D$55,"")</f>
-        <v>0.005976317397008333</v>
+        <v>0.006577382040332436</v>
       </c>
       <c r="H107" s="57" t="n">
         <f>IF(ISNUMBER(F107),F107*$D$45,"")</f>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I107" s="57" t="n">
         <f>IF(AND(ISNUMBER(H107),ISNUMBER($D$55)),H107*$D$55,"")</f>
-        <v>5976317.397008333</v>
+        <v>6577382.040332436</v>
       </c>
       <c r="J107" s="57" t="n">
         <f>IF(D107="","",E107-E106)</f>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="G108" s="60" t="n">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER($D$55)),F108*$D$55,"")</f>
-        <v>0.011007400920000118</v>
+        <v>0.01211446386000013</v>
       </c>
       <c r="H108" s="57" t="n">
         <f>IF(ISNUMBER(F108),F108*$D$45,"")</f>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="I108" s="57" t="n">
         <f>IF(AND(ISNUMBER(H108),ISNUMBER($D$55)),H108*$D$55,"")</f>
-        <v>11007400.92000012</v>
+        <v>12114463.860000132</v>
       </c>
       <c r="J108" s="57" t="n">
         <f>IF(D108="","",E108-E107)</f>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="G109" s="60" t="n">
         <f>IF(AND(ISNUMBER(F109),ISNUMBER($D$55)),F109*$D$55,"")</f>
-        <v>0.02663519234962997</v>
+        <v>0.02931401131555593</v>
       </c>
       <c r="H109" s="57" t="n">
         <f>IF(ISNUMBER(F109),F109*$D$45,"")</f>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="I109" s="57" t="n">
         <f>IF(AND(ISNUMBER(H109),ISNUMBER($D$55)),H109*$D$55,"")</f>
-        <v>26635192.34962997</v>
+        <v>29314011.31555593</v>
       </c>
       <c r="J109" s="57" t="n">
         <f>IF(D109="","",E109-E108)</f>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="G110" s="60" t="n">
         <f>IF(AND(ISNUMBER(F110),ISNUMBER($D$55)),F110*$D$55,"")</f>
-        <v>0.13484066126999675</v>
+        <v>0.1484021822849964</v>
       </c>
       <c r="H110" s="57" t="n">
         <f>IF(ISNUMBER(F110),F110*$D$45,"")</f>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="I110" s="57" t="n">
         <f>IF(AND(ISNUMBER(H110),ISNUMBER($D$55)),H110*$D$55,"")</f>
-        <v>134840661.26999673</v>
+        <v>148402182.28499642</v>
       </c>
       <c r="J110" s="57" t="n">
         <f>IF(D110="","",E110-E109)</f>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="G118" s="59" t="n">
         <f>IF(AND(ISNUMBER(F118),ISNUMBER($D$55)),F118*$D$55,"")</f>
-        <v>0.00005732412</v>
+        <v>0.00006308946</v>
       </c>
       <c r="H118" s="56" t="n">
         <f>IF(ISNUMBER(F118),F118*$D$45,"")</f>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I118" s="56" t="n">
         <f>IF(AND(ISNUMBER(H118),ISNUMBER($D$55)),H118*$D$55,"")</f>
-        <v>57324.12</v>
+        <v>63089.46000000001</v>
       </c>
       <c r="J118" s="53" t="n">
         <f>IF(H$118&gt;0,1-H118/H$118,"")</f>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="G119" s="60" t="n">
         <f>IF(AND(ISNUMBER(F119),ISNUMBER($D$55)),F119*$D$55,"")</f>
-        <v>0.00002601592277202833</v>
+        <v>0.000028632459060670627</v>
       </c>
       <c r="H119" s="57" t="n">
         <f>IF(ISNUMBER(F119),F119*$D$45,"")</f>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="I119" s="57" t="n">
         <f>IF(AND(ISNUMBER(H119),ISNUMBER($D$55)),H119*$D$55,"")</f>
-        <v>26015.922772028323</v>
+        <v>28632.459060670626</v>
       </c>
       <c r="J119" s="54" t="n">
         <f>IF(H$118&gt;0,1-H119/H$118,"")</f>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G120" s="60" t="n">
         <f>IF(AND(ISNUMBER(F120),ISNUMBER($D$55)),F120*$D$55,"")</f>
-        <v>0.000014789036286325034</v>
+        <v>0.000016276435001961686</v>
       </c>
       <c r="H120" s="57" t="n">
         <f>IF(ISNUMBER(F120),F120*$D$45,"")</f>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="I120" s="57" t="n">
         <f>IF(AND(ISNUMBER(H120),ISNUMBER($D$55)),H120*$D$55,"")</f>
-        <v>14789.036286325034</v>
+        <v>16276.435001961683</v>
       </c>
       <c r="J120" s="54" t="n">
         <f>IF(H$118&gt;0,1-H120/H$118,"")</f>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="G121" s="60" t="n">
         <f>IF(AND(ISNUMBER(F121),ISNUMBER($D$55)),F121*$D$55,"")</f>
-        <v>0.000009525293401870663</v>
+        <v>0.000010483294240985873</v>
       </c>
       <c r="H121" s="57" t="n">
         <f>IF(ISNUMBER(F121),F121*$D$45,"")</f>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="I121" s="57" t="n">
         <f>IF(AND(ISNUMBER(H121),ISNUMBER($D$55)),H121*$D$55,"")</f>
-        <v>9525.293401870662</v>
+        <v>10483.294240985873</v>
       </c>
       <c r="J121" s="54" t="n">
         <f>IF(H$118&gt;0,1-H121/H$118,"")</f>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="G122" s="60" t="n">
         <f>IF(AND(ISNUMBER(F122),ISNUMBER($D$55)),F122*$D$55,"")</f>
-        <v>0.000006642931366369693</v>
+        <v>0.000007311040321618999</v>
       </c>
       <c r="H122" s="57" t="n">
         <f>IF(ISNUMBER(F122),F122*$D$45,"")</f>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="I122" s="57" t="n">
         <f>IF(AND(ISNUMBER(H122),ISNUMBER($D$55)),H122*$D$55,"")</f>
-        <v>6642.931366369692</v>
+        <v>7311.040321618999</v>
       </c>
       <c r="J122" s="54" t="n">
         <f>IF(H$118&gt;0,1-H122/H$118,"")</f>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="G123" s="60" t="n">
         <f>IF(AND(ISNUMBER(F123),ISNUMBER($D$55)),F123*$D$55,"")</f>
-        <v>0.000004895371542494034</v>
+        <v>0.000005387720685730817</v>
       </c>
       <c r="H123" s="57" t="n">
         <f>IF(ISNUMBER(F123),F123*$D$45,"")</f>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I123" s="57" t="n">
         <f>IF(AND(ISNUMBER(H123),ISNUMBER($D$55)),H123*$D$55,"")</f>
-        <v>4895.371542494034</v>
+        <v>5387.720685730817</v>
       </c>
       <c r="J123" s="54" t="n">
         <f>IF(H$118&gt;0,1-H123/H$118,"")</f>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="G124" s="60" t="n">
         <f>IF(AND(ISNUMBER(F124),ISNUMBER($D$55)),F124*$D$55,"")</f>
-        <v>0.0000037565804036293793</v>
+        <v>0.000004134396290977682</v>
       </c>
       <c r="H124" s="57" t="n">
         <f>IF(ISNUMBER(F124),F124*$D$45,"")</f>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="I124" s="57" t="n">
         <f>IF(AND(ISNUMBER(H124),ISNUMBER($D$55)),H124*$D$55,"")</f>
-        <v>3756.5804036293794</v>
+        <v>4134.396290977683</v>
       </c>
       <c r="J124" s="54" t="n">
         <f>IF(H$118&gt;0,1-H124/H$118,"")</f>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G125" s="60" t="n">
         <f>IF(AND(ISNUMBER(F125),ISNUMBER($D$55)),F125*$D$55,"")</f>
-        <v>0.0000029734397694577518</v>
+        <v>0.00000327249174339901</v>
       </c>
       <c r="H125" s="57" t="n">
         <f>IF(ISNUMBER(F125),F125*$D$45,"")</f>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="I125" s="57" t="n">
         <f>IF(AND(ISNUMBER(H125),ISNUMBER($D$55)),H125*$D$55,"")</f>
-        <v>2973.439769457752</v>
+        <v>3272.4917433990104</v>
       </c>
       <c r="J125" s="54" t="n">
         <f>IF(H$118&gt;0,1-H125/H$118,"")</f>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G126" s="61" t="n">
         <f>IF(AND(ISNUMBER(F126),ISNUMBER($D$55)),F126*$D$55,"")</f>
-        <v>0.000002411914235599316</v>
+        <v>0.000002654491105842944</v>
       </c>
       <c r="H126" s="58" t="n">
         <f>IF(ISNUMBER(F126),F126*$D$45,"")</f>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="I126" s="58" t="n">
         <f>IF(AND(ISNUMBER(H126),ISNUMBER($D$55)),H126*$D$55,"")</f>
-        <v>2411.914235599316</v>
+        <v>2654.491105842944</v>
       </c>
       <c r="J126" s="55" t="n">
         <f>IF(H$118&gt;0,1-H126/H$118,"")</f>
@@ -4869,6 +4869,9 @@
     <x:col min="33" max="33" width="44" hidden="0" customWidth="1"/>
     <x:col min="34" max="34" width="20" hidden="0" customWidth="1"/>
     <x:col min="35" max="35" width="20" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="20" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="44" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
@@ -4907,6 +4910,9 @@
       <x:c r="AG1" s="5"/>
       <x:c r="AH1" s="5"/>
       <x:c r="AI1" s="5"/>
+      <x:c r="AJ1" s="5"/>
+      <x:c r="AK1" s="5"/>
+      <x:c r="AL1" s="5"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="5"/>
@@ -4946,6 +4952,9 @@
       <x:c r="AG2" s="7"/>
       <x:c r="AH2" s="7"/>
       <x:c r="AI2" s="7"/>
+      <x:c r="AJ2" s="7"/>
+      <x:c r="AK2" s="7"/>
+      <x:c r="AL2" s="7"/>
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="5"/>
@@ -4985,6 +4994,9 @@
       <x:c r="AG3" s="5"/>
       <x:c r="AH3" s="5"/>
       <x:c r="AI3" s="5"/>
+      <x:c r="AJ3" s="5"/>
+      <x:c r="AK3" s="5"/>
+      <x:c r="AL3" s="5"/>
     </x:row>
     <x:row r="4" ht="26" customHeight="1">
       <x:c r="A4" s="5"/>
@@ -5022,6 +5034,9 @@
       <x:c r="AG4" s="5"/>
       <x:c r="AH4" s="5"/>
       <x:c r="AI4" s="5"/>
+      <x:c r="AJ4" s="5"/>
+      <x:c r="AK4" s="5"/>
+      <x:c r="AL4" s="5"/>
     </x:row>
     <x:row r="5" ht="26" customHeight="1">
       <x:c r="A5" s="5"/>
@@ -5059,6 +5074,9 @@
       <x:c r="AG5" s="5"/>
       <x:c r="AH5" s="5"/>
       <x:c r="AI5" s="5"/>
+      <x:c r="AJ5" s="5"/>
+      <x:c r="AK5" s="5"/>
+      <x:c r="AL5" s="5"/>
     </x:row>
     <x:row r="6" ht="26" customHeight="1">
       <x:c r="A6" s="5"/>
@@ -5067,7 +5085,7 @@
         <x:v>USDT / USD</x:v>
       </x:c>
       <x:c r="D6" s="5" t="n">
-        <x:v>0.99917</x:v>
+        <x:v>0.999604</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
       <x:c r="F6" s="5"/>
@@ -5100,6 +5118,9 @@
       <x:c r="AG6" s="5"/>
       <x:c r="AH6" s="5"/>
       <x:c r="AI6" s="5"/>
+      <x:c r="AJ6" s="5"/>
+      <x:c r="AK6" s="5"/>
+      <x:c r="AL6" s="5"/>
     </x:row>
     <x:row r="7" ht="26" customHeight="1">
       <x:c r="A7" s="5"/>
@@ -5108,7 +5129,7 @@
         <x:v>快照时间 / UTC</x:v>
       </x:c>
       <x:c r="D7" s="6" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
       <x:c r="F7" s="5"/>
@@ -5141,6 +5162,9 @@
       <x:c r="AG7" s="5"/>
       <x:c r="AH7" s="5"/>
       <x:c r="AI7" s="5"/>
+      <x:c r="AJ7" s="5"/>
+      <x:c r="AK7" s="5"/>
+      <x:c r="AL7" s="5"/>
     </x:row>
     <x:row r="8" ht="26" customHeight="1">
       <x:c r="A8" s="5"/>
@@ -5182,6 +5206,9 @@
       <x:c r="AG8" s="5"/>
       <x:c r="AH8" s="5"/>
       <x:c r="AI8" s="5"/>
+      <x:c r="AJ8" s="5"/>
+      <x:c r="AK8" s="5"/>
+      <x:c r="AL8" s="5"/>
     </x:row>
     <x:row r="9" ht="26" customHeight="1">
       <x:c r="A9" s="5"/>
@@ -5219,6 +5246,9 @@
       <x:c r="AG9" s="5"/>
       <x:c r="AH9" s="5"/>
       <x:c r="AI9" s="5"/>
+      <x:c r="AJ9" s="5"/>
+      <x:c r="AK9" s="5"/>
+      <x:c r="AL9" s="5"/>
     </x:row>
     <x:row r="10" ht="26" customHeight="1">
       <x:c r="A10" s="5"/>
@@ -5260,6 +5290,9 @@
       <x:c r="AG10" s="5"/>
       <x:c r="AH10" s="5"/>
       <x:c r="AI10" s="5"/>
+      <x:c r="AJ10" s="5"/>
+      <x:c r="AK10" s="5"/>
+      <x:c r="AL10" s="5"/>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="5"/>
@@ -5268,7 +5301,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>损耗按目标加缓冲的 FDV × 双边费率。非 Pons 的补回按目标持仓洗一轮、小单固定价及现有外盘曲线差额估算；Pons 按原批准的 Quote 预算承担手续费，补回为 0。非逐笔模拟。</x:v>
+        <x:v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -5301,6 +5334,9 @@
       <x:c r="AG11" s="5"/>
       <x:c r="AH11" s="5"/>
       <x:c r="AI11" s="5"/>
+      <x:c r="AJ11" s="5"/>
+      <x:c r="AK11" s="5"/>
+      <x:c r="AL11" s="5"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
       <x:c r="A12" s="5"/>
@@ -5338,6 +5374,9 @@
       <x:c r="AG12" s="5"/>
       <x:c r="AH12" s="5"/>
       <x:c r="AI12" s="5"/>
+      <x:c r="AJ12" s="5"/>
+      <x:c r="AK12" s="5"/>
+      <x:c r="AL12" s="5"/>
     </x:row>
     <x:row r="13" ht="38" customHeight="1">
       <x:c r="A13" s="5"/>
@@ -5441,6 +5480,15 @@
       <x:c r="AI13" s="16" t="str">
         <x:v>单地址 Gas</x:v>
       </x:c>
+      <x:c r="AJ13" s="16" t="str">
+        <x:v>外盘扣费资产</x:v>
+      </x:c>
+      <x:c r="AK13" s="16" t="str">
+        <x:v>外盘扣费机制</x:v>
+      </x:c>
+      <x:c r="AL13" s="16" t="str">
+        <x:v>扣费机制来源</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="58" customHeight="1">
       <x:c r="A14" s="5"/>
@@ -5461,13 +5509,13 @@
         <x:v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</x:v>
       </x:c>
       <x:c r="H14" s="17" t="n">
-        <x:v>5.8494</x:v>
+        <x:v>6.4377</x:v>
       </x:c>
       <x:c r="I14" s="17" t="n">
-        <x:v>751.723930862616</x:v>
+        <x:v>752.7981080507881</x:v>
       </x:c>
       <x:c r="J14" s="6" t="n">
-        <x:v>46283.40053702546</x:v>
+        <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="K14" s="21" t="str">
         <x:v>https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:v>
@@ -5543,6 +5591,15 @@
       </x:c>
       <x:c r="AI14" s="5" t="n">
         <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="AJ14" s="18" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="AK14" s="21" t="str">
+        <x:v>PancakeSwap LP 费从输入币扣取；外盘买税扣输出 TOKEN，卖税扣输入 TOKEN</x:v>
+      </x:c>
+      <x:c r="AL14" s="21" t="str">
+        <x:v>https://docs.pancakeswap.finance/trade/pancakeswap-exchange/trade</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R07817fff46094703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R16d2ba0d60314fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R27bba28ac3784fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rd287077c4913490c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1039,7 +1039,7 @@
         <v>预算 91% 理论资金</v>
       </c>
       <c r="D22" s="44" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",$G$50/$J$51-$G$49,IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
+        <f>IF($D$51&lt;&gt;"可达","",$J$41+IF($G$40="pons",($G$50/$J$51-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",($G$50/$J$50-$G$49)/(1-$G$42),($G$50/$J$50-$G$49)*(1+$G$42))))</f>
         <v>4653.099415204678</v>
       </c>
       <c r="E22" s="3" t="str">
@@ -1599,8 +1599,8 @@
         <v>预算交换 TOKEN</v>
       </c>
       <c r="J51" s="32" t="n">
-        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$48)</f>
-        <v>89724310.77694237</v>
+        <f>$G$48-MAX(0,($D$52-$G$43)*$D$45)</f>
+        <v>90000000.00000001</v>
       </c>
       <c r="K51" s="32"/>
       <c r="L51" s="32"/>
@@ -1659,7 +1659,7 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="39" t="n">
-        <f>IF($G$40="pons",MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$48)*$G$48/$D$45),IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
+        <f>IF($G$40="pons",1-$G$51/$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$43+(1-$J$46)*$G$48/$D$45,1))</f>
         <v>0.994</v>
       </c>
       <c r="E54" s="32"/>
@@ -2235,7 +2235,7 @@
         <v>0.8</v>
       </c>
       <c r="D72" s="56" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C72)),C72&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C72-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C72-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C72)-$G$51,IF(ABS(C72-$G$43)&lt;0.000001,$G$48,$D$45*(1-C72)))))</f>
         <v>200000000</v>
       </c>
       <c r="E72" s="56" t="n">
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="L72" s="65" t="n">
-        <f>IF(D72="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C72-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
+        <f>IF(D72="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C72-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E72-$G$49)/(1-$G$42),(E72-$G$49)*(1+$G$42))))</f>
         <v>2080</v>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
         <v>0.805</v>
       </c>
       <c r="D73" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C73)),C73&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C73-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C73-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C73)-$G$51,IF(ABS(C73-$G$43)&lt;0.000001,$G$48,$D$45*(1-C73)))))</f>
         <v>194845360.82474226</v>
       </c>
       <c r="E73" s="57" t="n">
@@ -2309,7 +2309,7 @@
         <v>51.98180636777124</v>
       </c>
       <c r="L73" s="66" t="n">
-        <f>IF(D73="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
+        <f>IF(D73="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C73-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E73-$G$49)/(1-$G$42),(E73-$G$49)*(1+$G$42))))</f>
         <v>2131.9818063677712</v>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
         <v>0.81</v>
       </c>
       <c r="D74" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C74)),C74&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C74-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C74-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C74)-$G$51,IF(ABS(C74-$G$43)&lt;0.000001,$G$48,$D$45*(1-C74)))))</f>
         <v>189690721.64948452</v>
       </c>
       <c r="E74" s="57" t="n">
@@ -2351,7 +2351,7 @@
         <v>54.80690453993293</v>
       </c>
       <c r="L74" s="66" t="n">
-        <f>IF(D74="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
+        <f>IF(D74="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C74-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E74-$G$49)/(1-$G$42),(E74-$G$49)*(1+$G$42))))</f>
         <v>2186.788710907704</v>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
         <v>0.8150000000000001</v>
       </c>
       <c r="D75" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C75)),C75&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C75-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C75-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C75)-$G$51,IF(ABS(C75-$G$43)&lt;0.000001,$G$48,$D$45*(1-C75)))))</f>
         <v>184536082.4742268</v>
       </c>
       <c r="E75" s="57" t="n">
@@ -2393,7 +2393,7 @@
         <v>57.86874278238702</v>
       </c>
       <c r="L75" s="66" t="n">
-        <f>IF(D75="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
+        <f>IF(D75="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C75-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E75-$G$49)/(1-$G$42),(E75-$G$49)*(1+$G$42))))</f>
         <v>2244.657453690091</v>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="D76" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C76)),C76&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C76-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C76-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C76)-$G$51,IF(ABS(C76-$G$43)&lt;0.000001,$G$48,$D$45*(1-C76)))))</f>
         <v>179381443.29896906</v>
       </c>
       <c r="E76" s="57" t="n">
@@ -2435,7 +2435,7 @@
         <v>61.194532597466605</v>
       </c>
       <c r="L76" s="66" t="n">
-        <f>IF(D76="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
+        <f>IF(D76="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C76-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E76-$G$49)/(1-$G$42),(E76-$G$49)*(1+$G$42))))</f>
         <v>2305.851986287558</v>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
         <v>0.8250000000000001</v>
       </c>
       <c r="D77" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C77)),C77&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C77-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C77-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C77)-$G$51,IF(ABS(C77-$G$43)&lt;0.000001,$G$48,$D$45*(1-C77)))))</f>
         <v>174226804.12371132</v>
       </c>
       <c r="E77" s="57" t="n">
@@ -2477,7 +2477,7 @@
         <v>64.8155108576725</v>
       </c>
       <c r="L77" s="66" t="n">
-        <f>IF(D77="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
+        <f>IF(D77="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C77-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E77-$G$49)/(1-$G$42),(E77-$G$49)*(1+$G$42))))</f>
         <v>2370.6674971452303</v>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D78" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C78)),C78&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C78-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C78-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C78)-$G$51,IF(ABS(C78-$G$43)&lt;0.000001,$G$48,$D$45*(1-C78)))))</f>
         <v>169072164.94845358</v>
       </c>
       <c r="E78" s="57" t="n">
@@ -2519,7 +2519,7 @@
         <v>68.76767615387143</v>
       </c>
       <c r="L78" s="66" t="n">
-        <f>IF(D78="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
+        <f>IF(D78="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C78-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E78-$G$49)/(1-$G$42),(E78-$G$49)*(1+$G$42))))</f>
         <v>2439.4351732991017</v>
       </c>
     </row>
@@ -2529,7 +2529,7 @@
         <v>0.8350000000000001</v>
       </c>
       <c r="D79" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C79)),C79&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C79-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C79-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C79)-$G$51,IF(ABS(C79-$G$43)&lt;0.000001,$G$48,$D$45*(1-C79)))))</f>
         <v>163917525.77319586</v>
       </c>
       <c r="E79" s="57" t="n">
@@ -2561,7 +2561,7 @@
         <v>73.09268723273135</v>
       </c>
       <c r="L79" s="66" t="n">
-        <f>IF(D79="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
+        <f>IF(D79="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C79-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E79-$G$49)/(1-$G$42),(E79-$G$49)*(1+$G$42))))</f>
         <v>2512.527860531833</v>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
         <v>0.8400000000000001</v>
       </c>
       <c r="D80" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C80)),C80&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C80-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C80-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C80)-$G$51,IF(ABS(C80-$G$43)&lt;0.000001,$G$48,$D$45*(1-C80)))))</f>
         <v>158762886.59793812</v>
       </c>
       <c r="E80" s="57" t="n">
@@ -2603,7 +2603,7 @@
         <v>77.83896562446716</v>
       </c>
       <c r="L80" s="66" t="n">
-        <f>IF(D80="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
+        <f>IF(D80="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C80-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E80-$G$49)/(1-$G$42),(E80-$G$49)*(1+$G$42))))</f>
         <v>2590.3668261563002</v>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         <v>0.8450000000000001</v>
       </c>
       <c r="D81" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C81)),C81&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C81-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C81-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C81)-$G$51,IF(ABS(C81-$G$43)&lt;0.000001,$G$48,$D$45*(1-C81)))))</f>
         <v>153608247.42268038</v>
       </c>
       <c r="E81" s="57" t="n">
@@ -2645,7 +2645,7 @@
         <v>83.06305727711606</v>
       </c>
       <c r="L81" s="66" t="n">
-        <f>IF(D81="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
+        <f>IF(D81="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C81-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E81-$G$49)/(1-$G$42),(E81-$G$49)*(1+$G$42))))</f>
         <v>2673.4298834334163</v>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         <v>0.8500000000000001</v>
       </c>
       <c r="D82" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C82)),C82&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C82-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C82-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C82)-$G$51,IF(ABS(C82-$G$43)&lt;0.000001,$G$48,$D$45*(1-C82)))))</f>
         <v>148453608.24742264</v>
       </c>
       <c r="E82" s="57" t="n">
@@ -2687,7 +2687,7 @@
         <v>88.83132514358249</v>
       </c>
       <c r="L82" s="66" t="n">
-        <f>IF(D82="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
+        <f>IF(D82="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C82-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E82-$G$49)/(1-$G$42),(E82-$G$49)*(1+$G$42))))</f>
         <v>2762.261208576999</v>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         <v>0.8550000000000001</v>
       </c>
       <c r="D83" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C83)),C83&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C83-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C83-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C83)-$G$51,IF(ABS(C83-$G$43)&lt;0.000001,$G$48,$D$45*(1-C83)))))</f>
         <v>143298969.0721649</v>
       </c>
       <c r="E83" s="57" t="n">
@@ -2729,7 +2729,7 @@
         <v>95.22206795966758</v>
       </c>
       <c r="L83" s="66" t="n">
-        <f>IF(D83="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
+        <f>IF(D83="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C83-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E83-$G$49)/(1-$G$42),(E83-$G$49)*(1+$G$42))))</f>
         <v>2857.4832765366664</v>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>0.8600000000000001</v>
       </c>
       <c r="D84" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C84)),C84&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C84-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C84-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C84)-$G$51,IF(ABS(C84-$G$43)&lt;0.000001,$G$48,$D$45*(1-C84)))))</f>
         <v>138144329.89690715</v>
       </c>
       <c r="E84" s="57" t="n">
@@ -2771,7 +2771,7 @@
         <v>102.32819243426957</v>
       </c>
       <c r="L84" s="66" t="n">
-        <f>IF(D84="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
+        <f>IF(D84="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C84-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E84-$G$49)/(1-$G$42),(E84-$G$49)*(1+$G$42))))</f>
         <v>2959.811468970936</v>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         <v>0.865</v>
       </c>
       <c r="D85" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C85)),C85&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C85-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C85-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C85)-$G$51,IF(ABS(C85-$G$43)&lt;0.000001,$G$48,$D$45*(1-C85)))))</f>
         <v>132989690.72164953</v>
       </c>
       <c r="E85" s="57" t="n">
@@ -2813,7 +2813,7 @@
         <v>110.26061045242795</v>
       </c>
       <c r="L85" s="66" t="n">
-        <f>IF(D85="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
+        <f>IF(D85="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C85-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E85-$G$49)/(1-$G$42),(E85-$G$49)*(1+$G$42))))</f>
         <v>3070.072079423364</v>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
         <v>0.8700000000000001</v>
       </c>
       <c r="D86" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C86)),C86&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C86-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C86-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C86)-$G$51,IF(ABS(C86-$G$43)&lt;0.000001,$G$48,$D$45*(1-C86)))))</f>
         <v>127835051.5463917</v>
       </c>
       <c r="E86" s="57" t="n">
@@ -2855,7 +2855,7 @@
         <v>119.1525951663375</v>
       </c>
       <c r="L86" s="66" t="n">
-        <f>IF(D86="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C86-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
+        <f>IF(D86="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C86-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E86-$G$49)/(1-$G$42),(E86-$G$49)*(1+$G$42))))</f>
         <v>3189.2246745897014</v>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
         <v>0.875</v>
       </c>
       <c r="D87" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C87)),C87&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C87-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C87-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C87)-$G$51,IF(ABS(C87-$G$43)&lt;0.000001,$G$48,$D$45*(1-C87)))))</f>
         <v>122680412.37113406</v>
       </c>
       <c r="E87" s="57" t="n">
@@ -2897,7 +2897,7 @@
         <v>129.16541828955405</v>
       </c>
       <c r="L87" s="66" t="n">
-        <f>IF(D87="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C87-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
+        <f>IF(D87="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C87-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E87-$G$49)/(1-$G$42),(E87-$G$49)*(1+$G$42))))</f>
         <v>3318.3900928792555</v>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
         <v>0.88</v>
       </c>
       <c r="D88" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C88)),C88&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C88-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C88-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C88)-$G$51,IF(ABS(C88-$G$43)&lt;0.000001,$G$48,$D$45*(1-C88)))))</f>
         <v>117525773.19587633</v>
       </c>
       <c r="E88" s="57" t="n">
@@ -2939,7 +2939,7 @@
         <v>140.49571813951798</v>
       </c>
       <c r="L88" s="66" t="n">
-        <f>IF(D88="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C88-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
+        <f>IF(D88="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C88-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E88-$G$49)/(1-$G$42),(E88-$G$49)*(1+$G$42))))</f>
         <v>3458.8858110187734</v>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
         <v>0.885</v>
       </c>
       <c r="D89" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C89)),C89&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C89-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C89-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C89)-$G$51,IF(ABS(C89-$G$43)&lt;0.000001,$G$48,$D$45*(1-C89)))))</f>
         <v>112371134.02061859</v>
       </c>
       <c r="E89" s="57" t="n">
@@ -2981,7 +2981,7 @@
         <v>153.38523356516225</v>
       </c>
       <c r="L89" s="66" t="n">
-        <f>IF(D89="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C89-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
+        <f>IF(D89="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C89-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E89-$G$49)/(1-$G$42),(E89-$G$49)*(1+$G$42))))</f>
         <v>3612.2710445839357</v>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
         <v>0.89</v>
       </c>
       <c r="D90" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C90)),C90&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C90-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C90-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C90)-$G$51,IF(ABS(C90-$G$43)&lt;0.000001,$G$48,$D$45*(1-C90)))))</f>
         <v>107216494.84536086</v>
       </c>
       <c r="E90" s="57" t="n">
@@ -3023,7 +3023,7 @@
         <v>168.1338137156581</v>
       </c>
       <c r="L90" s="66" t="n">
-        <f>IF(D90="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C90-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
+        <f>IF(D90="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C90-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E90-$G$49)/(1-$G$42),(E90-$G$49)*(1+$G$42))))</f>
         <v>3780.404858299594</v>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
         <v>0.895</v>
       </c>
       <c r="D91" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C91)),C91&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C91-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C91-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C91)-$G$51,IF(ABS(C91-$G$43)&lt;0.000001,$G$48,$D$45*(1-C91)))))</f>
         <v>102061855.67010312</v>
       </c>
       <c r="E91" s="57" t="n">
@@ -3065,7 +3065,7 @@
         <v>185.11702722229074</v>
       </c>
       <c r="L91" s="66" t="n">
-        <f>IF(D91="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C91-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
+        <f>IF(D91="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C91-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E91-$G$49)/(1-$G$42),(E91-$G$49)*(1+$G$42))))</f>
         <v>3965.5218855218845</v>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
         <v>0.9</v>
       </c>
       <c r="D92" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C92)),C92&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C92-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C92-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C92)-$G$51,IF(ABS(C92-$G$43)&lt;0.000001,$G$48,$D$45*(1-C92)))))</f>
         <v>96907216.49484538</v>
       </c>
       <c r="E92" s="57" t="n">
@@ -3107,7 +3107,7 @@
         <v>204.81032799061904</v>
       </c>
       <c r="L92" s="66" t="n">
-        <f>IF(D92="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C92-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
+        <f>IF(D92="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C92-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E92-$G$49)/(1-$G$42),(E92-$G$49)*(1+$G$42))))</f>
         <v>4170.332213512504</v>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
         <v>0.905</v>
       </c>
       <c r="D93" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C93)),C93&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C93-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C93-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C93)-$G$51,IF(ABS(C93-$G$43)&lt;0.000001,$G$48,$D$45*(1-C93)))))</f>
         <v>91752577.31958765</v>
       </c>
       <c r="E93" s="57" t="n">
@@ -3149,7 +3149,7 @@
         <v>227.82272439406006</v>
       </c>
       <c r="L93" s="66" t="n">
-        <f>IF(D93="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C93-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
+        <f>IF(D93="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C93-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E93-$G$49)/(1-$G$42),(E93-$G$49)*(1+$G$42))))</f>
         <v>4398.154937906564</v>
       </c>
     </row>
@@ -3159,7 +3159,7 @@
         <v>0.91</v>
       </c>
       <c r="D94" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C94)),C94&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C94-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C94-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C94)-$G$51,IF(ABS(C94-$G$43)&lt;0.000001,$G$48,$D$45*(1-C94)))))</f>
         <v>86597938.1443299</v>
       </c>
       <c r="E94" s="57" t="n">
@@ -3191,7 +3191,7 @@
         <v>254.94447729811418</v>
       </c>
       <c r="L94" s="66" t="n">
-        <f>IF(D94="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C94-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
+        <f>IF(D94="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C94-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E94-$G$49)/(1-$G$42),(E94-$G$49)*(1+$G$42))))</f>
         <v>4653.099415204678</v>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
         <v>0.915</v>
       </c>
       <c r="D95" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C95)),C95&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C95-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C95-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C95)-$G$51,IF(ABS(C95-$G$43)&lt;0.000001,$G$48,$D$45*(1-C95)))))</f>
         <v>81443298.96907218</v>
       </c>
       <c r="E95" s="57" t="n">
@@ -3233,7 +3233,7 @@
         <v>287.2159301206593</v>
       </c>
       <c r="L95" s="66" t="n">
-        <f>IF(D95="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C95-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
+        <f>IF(D95="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C95-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E95-$G$49)/(1-$G$42),(E95-$G$49)*(1+$G$42))))</f>
         <v>4940.315345325337</v>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
         <v>0.92</v>
       </c>
       <c r="D96" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C96)),C96&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C96-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C96-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C96)-$G$51,IF(ABS(C96-$G$43)&lt;0.000001,$G$48,$D$45*(1-C96)))))</f>
         <v>76288659.79381444</v>
       </c>
       <c r="E96" s="57" t="n">
@@ -3275,7 +3275,7 @@
         <v>326.0288936504812</v>
       </c>
       <c r="L96" s="66" t="n">
-        <f>IF(D96="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C96-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
+        <f>IF(D96="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C96-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E96-$G$49)/(1-$G$42),(E96-$G$49)*(1+$G$42))))</f>
         <v>5266.344238975818</v>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>0.925</v>
       </c>
       <c r="D97" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C97)),C97&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C97-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C97-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C97)-$G$51,IF(ABS(C97-$G$43)&lt;0.000001,$G$48,$D$45*(1-C97)))))</f>
         <v>71134020.6185567</v>
       </c>
       <c r="E97" s="57" t="n">
@@ -3317,7 +3317,7 @@
         <v>373.27945794765037</v>
       </c>
       <c r="L97" s="66" t="n">
-        <f>IF(D97="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C97-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
+        <f>IF(D97="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C97-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E97-$G$49)/(1-$G$42),(E97-$G$49)*(1+$G$42))))</f>
         <v>5639.623696923469</v>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
         <v>0.93</v>
       </c>
       <c r="D98" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C98)),C98&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C98-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C98-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C98)-$G$51,IF(ABS(C98-$G$43)&lt;0.000001,$G$48,$D$45*(1-C98)))))</f>
         <v>65979381.443298966</v>
       </c>
       <c r="E98" s="57" t="n">
@@ -3359,7 +3359,7 @@
         <v>431.6043732519702</v>
       </c>
       <c r="L98" s="66" t="n">
-        <f>IF(D98="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C98-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
+        <f>IF(D98="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C98-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E98-$G$49)/(1-$G$42),(E98-$G$49)*(1+$G$42))))</f>
         <v>6071.228070175439</v>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
         <v>0.935</v>
       </c>
       <c r="D99" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C99)),C99&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C99-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C99-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C99)-$G$51,IF(ABS(C99-$G$43)&lt;0.000001,$G$48,$D$45*(1-C99)))))</f>
         <v>60824742.26804122</v>
       </c>
       <c r="E99" s="57" t="n">
@@ -3401,7 +3401,7 @@
         <v>504.75765685399983</v>
       </c>
       <c r="L99" s="66" t="n">
-        <f>IF(D99="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C99-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
+        <f>IF(D99="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C99-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E99-$G$49)/(1-$G$42),(E99-$G$49)*(1+$G$42))))</f>
         <v>6575.985727029439</v>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="D100" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C100)),C100&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C100-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C100-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C100)-$G$51,IF(ABS(C100-$G$43)&lt;0.000001,$G$48,$D$45*(1-C100)))))</f>
         <v>55670103.09278351</v>
       </c>
       <c r="E100" s="57" t="n">
@@ -3443,7 +3443,7 @@
         <v>598.2312970121457</v>
       </c>
       <c r="L100" s="66" t="n">
-        <f>IF(D100="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C100-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
+        <f>IF(D100="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C100-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E100-$G$49)/(1-$G$42),(E100-$G$49)*(1+$G$42))))</f>
         <v>7174.217024041584</v>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
         <v>0.9450000000000001</v>
       </c>
       <c r="D101" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C101)),C101&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C101-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C101-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C101)-$G$51,IF(ABS(C101-$G$43)&lt;0.000001,$G$48,$D$45*(1-C101)))))</f>
         <v>50515463.91752574</v>
       </c>
       <c r="E101" s="57" t="n">
@@ -3485,7 +3485,7 @@
         <v>720.3193168105508</v>
       </c>
       <c r="L101" s="66" t="n">
-        <f>IF(D101="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C101-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
+        <f>IF(D101="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C101-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E101-$G$49)/(1-$G$42),(E101-$G$49)*(1+$G$42))))</f>
         <v>7894.536340852135</v>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="D102" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C102)),C102&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C102-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C102-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C102)-$G$51,IF(ABS(C102-$G$43)&lt;0.000001,$G$48,$D$45*(1-C102)))))</f>
         <v>45360824.742267996</v>
       </c>
       <c r="E102" s="57" t="n">
@@ -3527,7 +3527,7 @@
         <v>884.0282524493086</v>
       </c>
       <c r="L102" s="66" t="n">
-        <f>IF(D102="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C102-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
+        <f>IF(D102="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C102-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E102-$G$49)/(1-$G$42),(E102-$G$49)*(1+$G$42))))</f>
         <v>8778.564593301444</v>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
         <v>0.9550000000000001</v>
       </c>
       <c r="D103" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C103)),C103&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C103-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C103-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C103)-$G$51,IF(ABS(C103-$G$43)&lt;0.000001,$G$48,$D$45*(1-C103)))))</f>
         <v>40206185.56701028</v>
       </c>
       <c r="E103" s="57" t="n">
@@ -3569,7 +3569,7 @@
         <v>1110.702163333739</v>
       </c>
       <c r="L103" s="66" t="n">
-        <f>IF(D103="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C103-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
+        <f>IF(D103="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C103-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E103-$G$49)/(1-$G$42),(E103-$G$49)*(1+$G$42))))</f>
         <v>9889.266756635183</v>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
         <v>0.9600000000000001</v>
       </c>
       <c r="D104" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C104)),C104&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C104-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C104-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C104)-$G$51,IF(ABS(C104-$G$43)&lt;0.000001,$G$48,$D$45*(1-C104)))))</f>
         <v>35051546.39175254</v>
       </c>
       <c r="E104" s="57" t="n">
@@ -3611,7 +3611,7 @@
         <v>1437.379270196614</v>
       </c>
       <c r="L104" s="66" t="n">
-        <f>IF(D104="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C104-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
+        <f>IF(D104="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C104-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E104-$G$49)/(1-$G$42),(E104-$G$49)*(1+$G$42))))</f>
         <v>11326.646026831797</v>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
         <v>0.9650000000000001</v>
       </c>
       <c r="D105" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C105)),C105&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C105-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C105-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C105)-$G$51,IF(ABS(C105-$G$43)&lt;0.000001,$G$48,$D$45*(1-C105)))))</f>
         <v>29896907.2164948</v>
       </c>
       <c r="E105" s="57" t="n">
@@ -3653,7 +3653,7 @@
         <v>1933.0272944023418</v>
       </c>
       <c r="L105" s="66" t="n">
-        <f>IF(D105="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C105-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
+        <f>IF(D105="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C105-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E105-$G$49)/(1-$G$42),(E105-$G$49)*(1+$G$42))))</f>
         <v>13259.673321234139</v>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>0.9700000000000001</v>
       </c>
       <c r="D106" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C106)),C106&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C106-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C106-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C106)-$G$51,IF(ABS(C106-$G$43)&lt;0.000001,$G$48,$D$45*(1-C106)))))</f>
         <v>24742268.041237086</v>
       </c>
       <c r="E106" s="57" t="n">
@@ -3695,7 +3695,7 @@
         <v>2738.455333736638</v>
       </c>
       <c r="L106" s="66" t="n">
-        <f>IF(D106="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C106-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
+        <f>IF(D106="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C106-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E106-$G$49)/(1-$G$42),(E106-$G$49)*(1+$G$42))))</f>
         <v>15998.128654970777</v>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
         <v>0.9750000000000001</v>
       </c>
       <c r="D107" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C107)),C107&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C107-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C107-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C107)-$G$51,IF(ABS(C107-$G$43)&lt;0.000001,$G$48,$D$45*(1-C107)))))</f>
         <v>19587628.865979344</v>
       </c>
       <c r="E107" s="57" t="n">
@@ -3737,7 +3737,7 @@
         <v>4179.7476146506815</v>
       </c>
       <c r="L107" s="66" t="n">
-        <f>IF(D107="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C107-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
+        <f>IF(D107="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C107-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E107-$G$49)/(1-$G$42),(E107-$G$49)*(1+$G$42))))</f>
         <v>20177.876269621458</v>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
         <v>0.9800000000000001</v>
       </c>
       <c r="D108" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C108)),C108&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C108-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C108-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C108)-$G$51,IF(ABS(C108-$G$43)&lt;0.000001,$G$48,$D$45*(1-C108)))))</f>
         <v>14432989.690721571</v>
       </c>
       <c r="E108" s="57" t="n">
@@ -3779,7 +3779,7 @@
         <v>7165.281625115527</v>
       </c>
       <c r="L108" s="66" t="n">
-        <f>IF(D108="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C108-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
+        <f>IF(D108="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C108-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E108-$G$49)/(1-$G$42),(E108-$G$49)*(1+$G$42))))</f>
         <v>27343.157894736985</v>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
         <v>0.9850000000000001</v>
       </c>
       <c r="D109" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C109)),C109&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C109-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C109-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C109)-$G$51,IF(ABS(C109-$G$43)&lt;0.000001,$G$48,$D$45*(1-C109)))))</f>
         <v>9278350.515463859</v>
       </c>
       <c r="E109" s="57" t="n">
@@ -3821,7 +3821,7 @@
         <v>15126.70565302157</v>
       </c>
       <c r="L109" s="66" t="n">
-        <f>IF(D109="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C109-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
+        <f>IF(D109="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C109-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E109-$G$49)/(1-$G$42),(E109-$G$49)*(1+$G$42))))</f>
         <v>42469.863547758556</v>
       </c>
     </row>
@@ -3831,7 +3831,7 @@
         <v>0.99</v>
       </c>
       <c r="D110" s="57" t="n">
-        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C110)),C110&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C110-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C110-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C110)-$G$51,IF(ABS(C110-$G$43)&lt;0.000001,$G$48,$D$45*(1-C110)))))</f>
         <v>4123711.3402062356</v>
       </c>
       <c r="E110" s="57" t="n">
@@ -3863,7 +3863,7 @@
         <v>52943.46978557362</v>
       </c>
       <c r="L110" s="66" t="n">
-        <f>IF(D110="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C110-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
+        <f>IF(D110="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C110-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E110-$G$49)/(1-$G$42),(E110-$G$49)*(1+$G$42))))</f>
         <v>95413.33333333218</v>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
         <v>0.9950000000000001</v>
       </c>
       <c r="D111" s="57" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C111)),C111&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C111-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C111-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C111)-$G$51,IF(ABS(C111-$G$43)&lt;0.000001,$G$48,$D$45*(1-C111)))))</f>
       </c>
       <c r="E111" s="57" t="str">
         <f>IF(D111="","",IF(ABS(C111-$G$43)&lt;0.000001,$G$49,$G$50/D111))</f>
@@ -3897,7 +3897,7 @@
         <f>IF(D111="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L111-L110,J111*(1+$G$42)))</f>
       </c>
       <c r="L111" s="66" t="str">
-        <f>IF(D111="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C111-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
+        <f>IF(D111="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C111-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E111-$G$49)/(1-$G$42),(E111-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -3906,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="57" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C112)),C112&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C112-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C112-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C112)-$G$51,IF(ABS(C112-$G$43)&lt;0.000001,$G$48,$D$45*(1-C112)))))</f>
       </c>
       <c r="E112" s="57" t="str">
         <f>IF(D112="","",IF(ABS(C112-$G$43)&lt;0.000001,$G$49,$G$50/D112))</f>
@@ -3930,7 +3930,7 @@
         <f>IF(D112="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L112-L111,J112*(1+$G$42)))</f>
       </c>
       <c r="L112" s="66" t="str">
-        <f>IF(D112="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C112-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
+        <f>IF(D112="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C112-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E112-$G$49)/(1-$G$42),(E112-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -3938,7 +3938,7 @@
         <f>IF($G$40="pons",80%+40*0.5%,IF(80.5%+40*0.5%&lt;=100%,80.5%+40*0.5%,""))</f>
       </c>
       <c r="D113" s="58" t="str">
-        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
+        <f>IF(OR(NOT(ISNUMBER(C113)),C113&gt;=$D$54,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113))))&lt;=0,AND($G$40="pons",$G$48-MAX(0,(C113-$G$43)*$D$45)&lt;=0)),"",IF(OR($G$40="flap",$G$40="four-stock"),$G$48-(C113-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-C113)-$G$51,IF(ABS(C113-$G$43)&lt;0.000001,$G$48,$D$45*(1-C113)))))</f>
       </c>
       <c r="E113" s="58" t="str">
         <f>IF(D113="","",IF(ABS(C113-$G$43)&lt;0.000001,$G$49,$G$50/D113))</f>
@@ -3962,7 +3962,7 @@
         <f>IF(D113="","",IF(OR(OR($G$40="flap",$G$40="four-stock"),$G$40="pons"),L113-L112,J113*(1+$G$42)))</f>
       </c>
       <c r="L113" s="67" t="str">
-        <f>IF(D113="","",$J$41+IF($G$40="pons",$G$50/($G$48-MAX(0,(C113-$G$43)*$D$45)/(1-$G$42-$J$48))-$G$49,IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
+        <f>IF(D113="","",$J$41+IF($G$40="pons",($G$50/($G$48-MAX(0,(C113-$G$43)*$D$45))-$G$49)/(1-$G$42-$J$48),IF($G$40="four-stock",(E113-$G$49)/(1-$G$42),(E113-$G$49)*(1+$G$42))))</f>
       </c>
     </row>
     <row r="114" ht="6" customHeight="1">

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R27bba28ac3784fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rd287077c4913490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R2661c30d3e144173"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R794630d80acc47bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -950,7 +950,7 @@
       </c>
       <c r="D18" s="43" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>13186.95699378578</v>
+        <v>11684.793859649122</v>
       </c>
       <c r="E18" s="31" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -972,7 +972,7 @@
       </c>
       <c r="J18" s="43" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>86549.82887660645</v>
+        <v>76879.35326797489</v>
       </c>
       <c r="K18" s="31" t="str">
         <v>USDT</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="D19" s="44" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>84893.67303889472</v>
+        <v>75223.19743026316</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1136,8 +1136,8 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",0,IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*IF($G$40="pons",1,IF($G$40="four-stock",1/(1-$G$42),1+$G$42))),"")))</f>
-        <v>1502.1631341366572</v>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
+        <v>0</v>
       </c>
       <c r="E26" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="D27" s="40" t="n">
         <f>D8*J54</f>
-        <v>0.8446929750000001</v>
+        <v>0.842450625</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1172,7 +1172,7 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="C28" s="3" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="38" t="n">
         <f>D8</f>
@@ -1231,7 +1231,7 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" ht="20" customHeight="1" hidden="1">
+    <row r="31" ht="20" hidden="1" customHeight="1">
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
@@ -1243,7 +1243,7 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" ht="20" customHeight="1" hidden="1">
+    <row r="32" ht="20" hidden="1" customHeight="1">
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
@@ -1255,7 +1255,7 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" ht="20" customHeight="1" hidden="1">
+    <row r="33" ht="20" hidden="1" customHeight="1">
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
@@ -1267,7 +1267,7 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" ht="20" customHeight="1" hidden="1">
+    <row r="34" ht="20" hidden="1" customHeight="1">
       <c r="C34"/>
       <c r="D34"/>
       <c r="E34"/>
@@ -1279,7 +1279,7 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" ht="20" customHeight="1" hidden="1">
+    <row r="35" ht="20" hidden="1" customHeight="1">
       <c r="C35"/>
       <c r="D35"/>
       <c r="E35"/>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘手续费只在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，损耗仍按目标加缓冲 FDV；非逐笔模拟。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1351,7 +1351,7 @@
       <c r="K39" s="14"/>
       <c r="L39" s="14"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
@@ -1368,7 +1368,7 @@
       <c r="K40" s="32"/>
       <c r="L40" s="32"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C41" s="32"/>
       <c r="D41" s="32"/>
       <c r="E41" s="32"/>
@@ -1390,7 +1390,7 @@
       <c r="K41" s="32"/>
       <c r="L41" s="32"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C42" s="32"/>
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
@@ -1407,7 +1407,7 @@
       <c r="K42" s="32"/>
       <c r="L42" s="32"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C43" s="32"/>
       <c r="D43" s="32"/>
       <c r="E43" s="32"/>
@@ -1429,7 +1429,7 @@
       <c r="K43" s="32"/>
       <c r="L43" s="32"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C44" s="32"/>
       <c r="D44" s="32"/>
       <c r="E44" s="32"/>
@@ -1451,7 +1451,7 @@
       <c r="K44" s="32"/>
       <c r="L44" s="32"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C45" s="32" t="str">
         <v>总供应量</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="K45" s="32"/>
       <c r="L45" s="32"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C46" s="32"/>
       <c r="D46" s="32"/>
       <c r="E46" s="32"/>
@@ -1500,7 +1500,7 @@
       <c r="K46" s="32"/>
       <c r="L46" s="32"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C47" s="32"/>
       <c r="D47" s="32"/>
       <c r="E47" s="32"/>
@@ -1517,7 +1517,7 @@
       <c r="K47" s="32"/>
       <c r="L47" s="32"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C48" s="32"/>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
@@ -1539,7 +1539,7 @@
       <c r="K48" s="32"/>
       <c r="L48" s="32"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C49" s="32"/>
       <c r="D49" s="32"/>
       <c r="E49" s="32"/>
@@ -1556,7 +1556,7 @@
       <c r="K49" s="32"/>
       <c r="L49" s="32"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C50" s="32"/>
       <c r="D50" s="32"/>
       <c r="E50" s="32"/>
@@ -1578,7 +1578,7 @@
       <c r="K50" s="32"/>
       <c r="L50" s="32"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C51" s="32" t="str">
         <v>目标是否可达</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="K51" s="32"/>
       <c r="L51" s="32"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C52" s="32" t="str">
         <v>预算控筹率</v>
       </c>
@@ -1632,7 +1632,7 @@
       <c r="K52" s="32"/>
       <c r="L52" s="32"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C53" s="32" t="str">
         <v>地址总数</v>
       </c>
@@ -1654,7 +1654,7 @@
       <c r="K53" s="32"/>
       <c r="L53" s="32"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C54" s="32" t="str">
         <v>当前控筹上限</v>
       </c>
@@ -1675,13 +1675,13 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="39" t="n">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,34,FALSE)="quote",1,IF($G$40="pons",MAX(0,1-MAX(0,$J$12)-$J$48),(1-$J$46)*(1-$J$47)*(1-MAX(0,$J$12))))</f>
-        <v>0.93854775</v>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
+        <v>0.93605625</v>
       </c>
       <c r="K54" s="32"/>
       <c r="L54" s="32"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C55" s="32" t="str">
         <v>有效价格 / USDT</v>
       </c>
@@ -1708,7 +1708,7 @@
       <c r="K55" s="32"/>
       <c r="L55" s="32"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="C56" s="32" t="str">
         <v>价格时间 / UTC</v>
       </c>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J56" s="32" t="n">
         <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
-        <v>153924768.0412371</v>
+        <v>156236469.07216498</v>
       </c>
       <c r="K56" s="32"/>
       <c r="L56" s="32"/>
@@ -5084,7 +5084,7 @@
       <x:c r="C6" s="5" t="str">
         <x:v>USDT / USD</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="n">
+      <x:c r="D6" s="5">
         <x:v>0.999604</x:v>
       </x:c>
       <x:c r="E6" s="5"/>
@@ -5128,7 +5128,7 @@
       <x:c r="C7" s="5" t="str">
         <x:v>快照时间 / UTC</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="n">
+      <x:c r="D7" s="6">
         <x:v>46285.27349457176</x:v>
       </x:c>
       <x:c r="E7" s="5"/>
@@ -5172,8 +5172,10 @@
       <x:c r="C8" s="5" t="str">
         <x:v>汇率来源</x:v>
       </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:v>
+      <x:c r="D8" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" s="5"/>
       <x:c r="F8" s="5"/>
@@ -5301,7 +5303,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>损耗按目标加缓冲的 FDV × 双边费率。外盘手续费仅在扣 Base/TOKEN 时降低控筹率；只扣 Quote 时补回为 0。补回按 Base/TOKEN 缺口及现有外盘曲线差额估算，非逐笔模拟。</x:v>
+        <x:v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
@@ -5508,17 +5510,19 @@
       <x:c r="G14" s="21" t="str">
         <x:v>0x7c8d5502b544ddaf8852fc46d1174e34876d545c</x:v>
       </x:c>
-      <x:c r="H14" s="17" t="n">
+      <x:c r="H14" s="17">
         <x:v>6.4377</x:v>
       </x:c>
-      <x:c r="I14" s="17" t="n">
+      <x:c r="I14" s="17">
         <x:v>752.7981080507881</x:v>
       </x:c>
-      <x:c r="J14" s="6" t="n">
+      <x:c r="J14" s="6">
         <x:v>46285.27349457176</x:v>
       </x:c>
-      <x:c r="K14" s="21" t="str">
-        <x:v>https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:v>
+      <x:c r="K14" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://dexscreener.com/bsc/0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:t>
+        </x:is>
       </x:c>
       <x:c r="L14" s="18" t="str">
         <x:v>four-stock</x:v>
@@ -5580,11 +5584,15 @@
       <x:c r="AE14" s="5" t="str">
         <x:v>2026-09-16</x:v>
       </x:c>
-      <x:c r="AF14" s="21" t="str">
-        <x:v>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:v>
-      </x:c>
-      <x:c r="AG14" s="21" t="str">
-        <x:v>0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:v>
+      <x:c r="AF14" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AG14" s="21" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0xbec6906a984f4695aca0f15bafa7de5eb45b54ab</x:t>
+        </x:is>
       </x:c>
       <x:c r="AH14" s="19" t="n">
         <x:v>0.1</x:v>

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R2661c30d3e144173"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R794630d80acc47bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Re97bbfe24f004914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R792cbd5cf8404b1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -950,7 +950,7 @@
       </c>
       <c r="D18" s="43" t="n">
         <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>11684.793859649122</v>
+        <v>13224.732814291605</v>
       </c>
       <c r="E18" s="31" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -972,7 +972,7 @@
       </c>
       <c r="J18" s="43" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>76879.35326797489</v>
+        <v>86793.01827627681</v>
       </c>
       <c r="K18" s="31" t="str">
         <v>USDT</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="D19" s="44" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>75223.19743026316</v>
+        <v>85136.86243856508</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1136,8 +1136,8 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="44" t="n">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
-        <v>0</v>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(IF($G$40="pons",1/(1-$G$42-$J$48),IF($G$40="four-stock",1/(1-$G$42),1+$G$42)))),""))</f>
+        <v>1539.9389546424832</v>
       </c>
       <c r="E26" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -1293,7 +1293,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -1702,7 +1702,7 @@
         <v>目标外盘 TOKEN</v>
       </c>
       <c r="J55" s="32" t="n">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$8)-$G$51,IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$8-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$8-$G$43)*$D$45/(1-$J$46),IF(ABS($D$8-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$8))))</f>
         <v>96907216.49484538</v>
       </c>
       <c r="K55" s="32"/>
@@ -1729,7 +1729,7 @@
         <v>洗后外盘 TOKEN</v>
       </c>
       <c r="J56" s="32" t="n">
-        <f>IF($G$40="pons",$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$48),IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF($G$40="pons",$D$45*(1-$D$27)-$G$51,IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27)))))</f>
+        <f>IF($G$40="pons",$G$48-($D$27-$G$43)*$D$45,IF(OR($G$40="flap",$G$40="four-stock"),$G$48-($D$27-$G$43)*$D$45/(1-$J$46),IF(ABS($D$27-$G$43)&lt;0.000001,$G$48,$D$45*(1-$D$27))))</f>
         <v>156236469.07216498</v>
       </c>
       <c r="K56" s="32"/>
@@ -5303,7 +5303,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>外盘一卖一买，卖出所得 Quote 全额用于回买。洗后控筹按双边含税费率同价估算，额外补回预留为 0；洗筹损耗预算另列，不计滑点与冲击。</x:v>
+        <x:v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>

--- a/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
+++ b/excel/templates/FourMeme_4Stock_BNC4_控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="Re97bbfe24f004914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="R792cbd5cf8404b1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="控筹模型" sheetId="1" r:id="R7df17c9a95394e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quote参数" sheetId="2" r:id="Rd163d6e651494776"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="7">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <x:numFmt numFmtId="201" formatCode="0.0000000000"/>
     <x:numFmt numFmtId="202" formatCode="@"/>
@@ -22,6 +22,7 @@
     <x:numFmt numFmtId="204" formatCode="#,##0"/>
     <x:numFmt numFmtId="205" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="206" formatCode="0.0000%"/>
+    <x:numFmt numFmtId="207" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -155,7 +156,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -350,6 +351,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="204" fontId="11" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -949,8 +953,8 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="43" t="n">
-        <f>IF(AND($D$51="可达",ISNUMBER($D$26)),SUM(D22:D26),"")</f>
-        <v>13224.732814291605</v>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
+        <v>9827.038369847161</v>
       </c>
       <c r="E18" s="31" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
@@ -972,7 +976,7 @@
       </c>
       <c r="J18" s="43" t="n">
         <f>IF(AND(ISNUMBER(D19),ISNUMBER(G19)),SUM(D19,G19),"")</f>
-        <v>86793.01827627681</v>
+        <v>64919.68075127681</v>
       </c>
       <c r="K18" s="31" t="str">
         <v>USDT</v>
@@ -985,7 +989,7 @@
       </c>
       <c r="D19" s="44" t="n">
         <f>IF(ISNUMBER(D18),IF(D18=0,0,IF(D55&gt;0,D18*D55,"")),"")</f>
-        <v>85136.86243856508</v>
+        <v>63263.524913565074</v>
       </c>
       <c r="E19" s="3" t="str">
         <v>USDT</v>
@@ -1081,14 +1085,9 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="C24" s="3" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="44" t="n">
-        <f>IF($D$51="可达",$J$52*$D$29,"")</f>
-        <v>3397.694444444444</v>
-      </c>
+    <row r="24" customHeight="1" hidden="1">
+      <c r="C24" s="3"/>
+      <c r="D24" s="68"/>
       <c r="E24" s="3" t="str">
         <f>VLOOKUP($D$7,'Quote参数'!$C$14:$AL$14,3,FALSE)</f>
         <v>BNC4</v>
@@ -1293,7 +1292,7 @@
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="C36" s="25" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -5303,7 +5302,7 @@
         <x:v>洗筹与补回口径</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>外盘一卖一买用卖出所得 Quote 回买；洗后持币按双边费率估算，再按外盘曲线和买入费预留恢复目标所需 Quote。洗筹损耗另列。</x:v>
+        <x:v>外盘一卖一买用卖出所得 Quote 回买；双边费用仅降低洗后持币，不另列资金；只按外盘曲线和买入费预留恢复目标所需 Quote。</x:v>
       </x:c>
       <x:c r="E11" s="12"/>
       <x:c r="F11" s="12"/>
